--- a/youzi/落升(江南神鹰)/index.xlsx
+++ b/youzi/落升(江南神鹰)/index.xlsx
@@ -39,19 +39,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,7 +117,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -81,13 +141,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -111,12 +231,288 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -129,6 +525,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -147,6 +555,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -159,1195 +585,769 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3898,7 +3898,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="8" t="str">
         <v>净买: 1815.37万</v>
       </c>
       <c r="E2">
@@ -3913,37 +3913,37 @@
       <c r="H2">
         <v>10.02</v>
       </c>
-      <c r="I2" s="13">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
-      <c r="J2" s="8">
+      <c r="J2" s="10">
         <v>2.04</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="11">
         <v>4.88</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="13">
         <v>7.07</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="1">
         <v>7.94</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="2">
         <v>10.06</v>
       </c>
-      <c r="O2" s="4">
+      <c r="O2" s="3">
         <v>21.06</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="5">
         <v>33.16</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="4">
         <v>23.03</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="6">
         <v>25.8</v>
       </c>
-      <c r="S2" s="11">
+      <c r="S2" s="12">
         <v>24.05</v>
       </c>
       <c r="T2" s="7">
@@ -3960,7 +3960,7 @@
       <c r="C3" t="str">
         <v>605588</v>
       </c>
-      <c r="D3" s="21" t="str">
+      <c r="D3" s="15" t="str">
         <v>净买: 1980.32万</v>
       </c>
       <c r="E3">
@@ -3975,40 +3975,40 @@
       <c r="H3">
         <v>10.01</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="24">
         <v>0</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="16">
         <v>6.96</v>
       </c>
-      <c r="K3" s="23">
+      <c r="K3" s="22">
         <v>6.11</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="23">
         <v>-2.38</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="26">
         <v>-10.29</v>
       </c>
-      <c r="N3" s="15">
+      <c r="N3" s="17">
         <v>-19.26</v>
       </c>
-      <c r="O3" s="14">
+      <c r="O3" s="18">
         <v>-18.34</v>
       </c>
-      <c r="P3" s="16">
+      <c r="P3" s="19">
         <v>-18.05</v>
       </c>
-      <c r="Q3" s="19">
+      <c r="Q3" s="25">
         <v>-17.13</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="20">
         <v>-13.31</v>
       </c>
-      <c r="S3" s="20">
+      <c r="S3" s="21">
         <v>-13.66</v>
       </c>
-      <c r="T3" s="24">
+      <c r="T3" s="14">
         <v>4.46</v>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       <c r="C4" t="str">
         <v>002165</v>
       </c>
-      <c r="D4" s="27" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 3957.43万</v>
       </c>
       <c r="E4">
@@ -4037,40 +4037,40 @@
       <c r="H4">
         <v>-10.02</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="33">
         <v>22.26</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="38">
         <v>16.61</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="30">
         <v>28.28</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="39">
         <v>18.25</v>
       </c>
       <c r="M4" s="34">
         <v>30.11</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="27">
         <v>29.56</v>
       </c>
-      <c r="O4" s="35">
+      <c r="O4" s="28">
         <v>32.48</v>
       </c>
       <c r="P4" s="36">
         <v>40.15</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="35">
         <v>48.54</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="29">
         <v>63.32</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="37">
         <v>79.74</v>
       </c>
-      <c r="T4" s="39">
+      <c r="T4" s="31">
         <v>77.55</v>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       <c r="C5" t="str">
         <v>002165</v>
       </c>
-      <c r="D5" s="41" t="str">
+      <c r="D5" s="51" t="str">
         <v>净卖: -4519.88万</v>
       </c>
       <c r="E5">
@@ -4099,40 +4099,40 @@
       <c r="H5">
         <v>-8.21</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="52">
         <v>3.9</v>
       </c>
       <c r="J5" s="50">
         <v>14.31</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="48">
         <v>5.37</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="49">
         <v>15.93</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="40">
         <v>15.45</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="41">
         <v>18.05</v>
       </c>
       <c r="O5" s="45">
         <v>24.88</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="42">
         <v>32.36</v>
       </c>
-      <c r="Q5" s="52">
+      <c r="Q5" s="46">
         <v>45.53</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="43">
         <v>60.16</v>
       </c>
-      <c r="S5" s="48">
+      <c r="S5" s="47">
         <v>76.26</v>
       </c>
-      <c r="T5" s="49">
+      <c r="T5" s="44">
         <v>58.21</v>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 1976.41万</v>
       </c>
       <c r="E6">
@@ -4161,40 +4161,40 @@
       <c r="H6">
         <v>10</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="58">
         <v>0</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="61">
         <v>9.93</v>
       </c>
-      <c r="K6" s="63">
+      <c r="K6" s="59">
         <v>20.88</v>
       </c>
-      <c r="L6" s="64">
+      <c r="L6" s="53">
         <v>33</v>
       </c>
-      <c r="M6" s="65">
+      <c r="M6" s="62">
         <v>43.1</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="54">
         <v>28.79</v>
       </c>
-      <c r="O6" s="53">
+      <c r="O6" s="60">
         <v>19.36</v>
       </c>
-      <c r="P6" s="54">
+      <c r="P6" s="55">
         <v>21.55</v>
       </c>
-      <c r="Q6" s="59">
+      <c r="Q6" s="56">
         <v>9.43</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="64">
         <v>4.04</v>
       </c>
-      <c r="S6" s="60">
+      <c r="S6" s="63">
         <v>4.38</v>
       </c>
-      <c r="T6" s="61">
+      <c r="T6" s="57">
         <v>-1.18</v>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="72" t="str">
+      <c r="D7" s="68" t="str">
         <v>净卖: -2117.52万</v>
       </c>
       <c r="E7">
@@ -4223,40 +4223,40 @@
       <c r="H7">
         <v>7.72</v>
       </c>
-      <c r="I7" s="73">
+      <c r="I7" s="66">
         <v>2.15</v>
       </c>
-      <c r="J7" s="68">
+      <c r="J7" s="74">
         <v>1.72</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="69">
         <v>4.01</v>
       </c>
-      <c r="L7" s="69">
+      <c r="L7" s="70">
         <v>10.03</v>
       </c>
-      <c r="M7" s="74">
+      <c r="M7" s="67">
         <v>16.62</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="71">
         <v>28.22</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="77">
         <v>41.12</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="75">
         <v>55.3</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="72">
         <v>70.77</v>
       </c>
-      <c r="R7" s="71">
+      <c r="R7" s="76">
         <v>73.21</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="78">
         <v>90.54</v>
       </c>
-      <c r="T7" s="66">
+      <c r="T7" s="73">
         <v>39.4</v>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       <c r="C8" t="str">
         <v>002923</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="82" t="str">
         <v>净买: 1689.05万</v>
       </c>
       <c r="E8">
@@ -4285,40 +4285,40 @@
       <c r="H8">
         <v>-5.06</v>
       </c>
-      <c r="I8" s="83">
+      <c r="I8" s="88">
         <v>-5.2</v>
       </c>
       <c r="J8" s="79">
         <v>-2.53</v>
       </c>
-      <c r="K8" s="86">
+      <c r="K8" s="83">
         <v>-6.53</v>
       </c>
       <c r="L8" s="87">
         <v>-6.07</v>
       </c>
-      <c r="M8" s="84">
+      <c r="M8" s="89">
         <v>-4.07</v>
       </c>
-      <c r="N8" s="88">
+      <c r="N8" s="80">
         <v>-13.67</v>
       </c>
-      <c r="O8" s="80">
+      <c r="O8" s="84">
         <v>-17</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="85">
         <v>-19.33</v>
       </c>
-      <c r="Q8" s="82">
+      <c r="Q8" s="90">
         <v>-16</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="81">
         <v>-17.47</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="86">
         <v>-15</v>
       </c>
-      <c r="T8" s="90">
+      <c r="T8" s="91">
         <v>-16.27</v>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       <c r="C9" t="str">
         <v>000965</v>
       </c>
-      <c r="D9" s="100" t="str">
+      <c r="D9" s="103" t="str">
         <v>净卖: -66.63万</v>
       </c>
       <c r="E9">
@@ -4347,40 +4347,40 @@
       <c r="H9">
         <v>0.31</v>
       </c>
-      <c r="I9" s="93">
+      <c r="I9" s="96">
         <v>8.75</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="104">
         <v>-1.56</v>
       </c>
-      <c r="K9" s="101">
+      <c r="K9" s="93">
         <v>-0.94</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="100">
         <v>-3.75</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="97">
         <v>5.94</v>
       </c>
-      <c r="N9" s="97">
+      <c r="N9" s="101">
         <v>16.56</v>
       </c>
       <c r="O9" s="98">
         <v>28.12</v>
       </c>
-      <c r="P9" s="103">
+      <c r="P9" s="94">
         <v>40.94</v>
       </c>
-      <c r="Q9" s="104">
+      <c r="Q9" s="92">
         <v>55</v>
       </c>
-      <c r="R9" s="94">
+      <c r="R9" s="102">
         <v>48.12</v>
       </c>
-      <c r="S9" s="95">
+      <c r="S9" s="99">
         <v>62.81</v>
       </c>
-      <c r="T9" s="92">
+      <c r="T9" s="95">
         <v>14.06</v>
       </c>
     </row>
@@ -4409,25 +4409,25 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="105">
+      <c r="I10" s="115">
         <v>-0.74</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="116">
         <v>-10.6</v>
       </c>
       <c r="K10" s="106">
         <v>-14.1</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="117">
         <v>-12.78</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="112">
         <v>-4.07</v>
       </c>
-      <c r="N10" s="113">
+      <c r="N10" s="107">
         <v>-3.06</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="113">
         <v>-6.09</v>
       </c>
       <c r="P10" s="108">
@@ -4436,13 +4436,13 @@
       <c r="Q10" s="109">
         <v>-2.01</v>
       </c>
-      <c r="R10" s="110">
+      <c r="R10" s="105">
         <v>-1.88</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="110">
         <v>-4.77</v>
       </c>
-      <c r="T10" s="117">
+      <c r="T10" s="114">
         <v>6.87</v>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       <c r="C11" t="str">
         <v>600794</v>
       </c>
-      <c r="D11" s="127" t="str">
+      <c r="D11" s="118" t="str">
         <v>净卖: -697.77万</v>
       </c>
       <c r="E11">
@@ -4471,40 +4471,40 @@
       <c r="H11">
         <v>-8.75</v>
       </c>
-      <c r="I11" s="122">
+      <c r="I11" s="127">
         <v>-1.46</v>
       </c>
-      <c r="J11" s="119">
+      <c r="J11" s="122">
         <v>-11.25</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="123">
         <v>-17.08</v>
       </c>
       <c r="L11" s="128">
         <v>-14.37</v>
       </c>
-      <c r="M11" s="129">
+      <c r="M11" s="121">
         <v>-11.67</v>
       </c>
-      <c r="N11" s="123">
+      <c r="N11" s="129">
         <v>-12.71</v>
       </c>
-      <c r="O11" s="120">
+      <c r="O11" s="119">
         <v>-15.42</v>
       </c>
-      <c r="P11" s="130">
+      <c r="P11" s="120">
         <v>-15.42</v>
       </c>
       <c r="Q11" s="124">
         <v>-12.29</v>
       </c>
-      <c r="R11" s="126">
+      <c r="R11" s="125">
         <v>-3.54</v>
       </c>
-      <c r="S11" s="121">
+      <c r="S11" s="130">
         <v>-0.83</v>
       </c>
-      <c r="T11" s="118">
+      <c r="T11" s="126">
         <v>-25</v>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       <c r="C12" t="str">
         <v>000627</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 1535.97万</v>
       </c>
       <c r="E12">
@@ -4533,40 +4533,40 @@
       <c r="H12">
         <v>-9.87</v>
       </c>
-      <c r="I12" s="132">
+      <c r="I12" s="141">
         <v>0</v>
       </c>
-      <c r="J12" s="138">
+      <c r="J12" s="142">
         <v>-5.11</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="133">
         <v>-9.85</v>
       </c>
-      <c r="L12" s="133">
+      <c r="L12" s="139">
         <v>-14.23</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="136">
         <v>-18.61</v>
       </c>
-      <c r="N12" s="134">
+      <c r="N12" s="140">
         <v>-22.63</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="134">
         <v>-26.64</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="143">
         <v>-30.29</v>
       </c>
-      <c r="Q12" s="143">
+      <c r="Q12" s="137">
         <v>-33.94</v>
       </c>
-      <c r="R12" s="137">
+      <c r="R12" s="131">
         <v>-36.86</v>
       </c>
-      <c r="S12" s="131">
+      <c r="S12" s="132">
         <v>-36.86</v>
       </c>
-      <c r="T12" s="141">
+      <c r="T12" s="138">
         <v>-42.34</v>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="C13" t="str">
         <v>603669</v>
       </c>
-      <c r="D13" s="150" t="str">
+      <c r="D13" s="148" t="str">
         <v>净卖: -338.04万</v>
       </c>
       <c r="E13">
@@ -4595,40 +4595,40 @@
       <c r="H13">
         <v>0.7</v>
       </c>
-      <c r="I13" s="144">
+      <c r="I13" s="153">
         <v>9.25</v>
       </c>
-      <c r="J13" s="151">
+      <c r="J13" s="149">
         <v>9.77</v>
       </c>
-      <c r="K13" s="148">
+      <c r="K13" s="150">
         <v>10.65</v>
       </c>
-      <c r="L13" s="152">
+      <c r="L13" s="154">
         <v>8.9</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="155">
         <v>8.2</v>
       </c>
-      <c r="N13" s="146">
+      <c r="N13" s="151">
         <v>7.33</v>
       </c>
-      <c r="O13" s="147">
+      <c r="O13" s="156">
         <v>4.36</v>
       </c>
-      <c r="P13" s="155">
+      <c r="P13" s="145">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="144">
         <v>1.05</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="146">
         <v>4.71</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="152">
         <v>3.84</v>
       </c>
-      <c r="T13" s="154">
+      <c r="T13" s="147">
         <v>-22.69</v>
       </c>
     </row>
@@ -4660,34 +4660,34 @@
       <c r="I14" s="169">
         <v>-0.7</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="162">
         <v>-3</v>
       </c>
-      <c r="K14" s="165">
+      <c r="K14" s="157">
         <v>-4.4</v>
       </c>
-      <c r="L14" s="166">
+      <c r="L14" s="159">
         <v>-2.57</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="163">
         <v>-6.27</v>
       </c>
-      <c r="N14" s="161">
+      <c r="N14" s="160">
         <v>-6.34</v>
       </c>
-      <c r="O14" s="157">
+      <c r="O14" s="165">
         <v>-10.14</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="158">
         <v>-5.84</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="166">
         <v>-7.84</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="161">
         <v>-9.34</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="164">
         <v>-8.27</v>
       </c>
       <c r="T14" s="167">
@@ -4704,7 +4704,7 @@
       <c r="C15" t="str">
         <v>002856</v>
       </c>
-      <c r="D15" s="171" t="str">
+      <c r="D15" s="182" t="str">
         <v>净买: 611.16万</v>
       </c>
       <c r="E15">
@@ -4719,40 +4719,40 @@
       <c r="H15">
         <v>-6.28</v>
       </c>
-      <c r="I15" s="181">
+      <c r="I15" s="178">
         <v>17.36</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="170">
         <v>12.95</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="171">
         <v>15.42</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="172">
         <v>15.86</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="173">
         <v>13.22</v>
       </c>
-      <c r="N15" s="182">
+      <c r="N15" s="175">
         <v>9.87</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="179">
         <v>15.95</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="176">
         <v>16.56</v>
       </c>
-      <c r="Q15" s="176">
+      <c r="Q15" s="180">
         <v>14.8</v>
       </c>
-      <c r="R15" s="177">
+      <c r="R15" s="181">
         <v>11.45</v>
       </c>
-      <c r="S15" s="179">
+      <c r="S15" s="174">
         <v>5.55</v>
       </c>
-      <c r="T15" s="180">
+      <c r="T15" s="177">
         <v>1.76</v>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       <c r="C16" t="str">
         <v>603017</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="195" t="str">
         <v>净买: 1022.95万</v>
       </c>
       <c r="E16">
@@ -4781,40 +4781,40 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="191">
+      <c r="I16" s="183">
         <v>0</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="191">
         <v>10</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="187">
         <v>-0.98</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="188">
         <v>-6.69</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="184">
         <v>-9.32</v>
       </c>
-      <c r="N16" s="184">
+      <c r="N16" s="185">
         <v>-9.55</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="192">
         <v>-8.87</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="193">
         <v>-9.25</v>
       </c>
-      <c r="Q16" s="189">
+      <c r="Q16" s="186">
         <v>-7.74</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="189">
         <v>-3.68</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="194">
         <v>-4.59</v>
       </c>
-      <c r="T16" s="185">
+      <c r="T16" s="190">
         <v>-2.86</v>
       </c>
     </row>
@@ -4877,40 +4877,40 @@
       <c r="F18" t="str"/>
       <c r="G18" t="str"/>
       <c r="H18" t="str"/>
-      <c r="I18" s="205">
+      <c r="I18" s="196">
         <v>40</v>
       </c>
-      <c r="J18" s="198">
+      <c r="J18" s="205">
         <v>60</v>
       </c>
-      <c r="K18" s="203">
+      <c r="K18" s="202">
         <v>53.33</v>
       </c>
-      <c r="L18" s="199">
+      <c r="L18" s="206">
         <v>46.67</v>
       </c>
-      <c r="M18" s="200">
+      <c r="M18" s="197">
         <v>53.33</v>
       </c>
-      <c r="N18" s="206">
+      <c r="N18" s="201">
         <v>53.33</v>
       </c>
-      <c r="O18" s="207">
+      <c r="O18" s="198">
         <v>53.33</v>
       </c>
-      <c r="P18" s="201">
+      <c r="P18" s="199">
         <v>60</v>
       </c>
-      <c r="Q18" s="202">
+      <c r="Q18" s="203">
         <v>53.33</v>
       </c>
-      <c r="R18" s="196">
+      <c r="R18" s="207">
         <v>53.33</v>
       </c>
-      <c r="S18" s="204">
+      <c r="S18" s="200">
         <v>53.33</v>
       </c>
-      <c r="T18" s="197">
+      <c r="T18" s="204">
         <v>46.67</v>
       </c>
     </row>
@@ -4925,40 +4925,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="212">
+      <c r="I19" s="216">
         <v>3.7</v>
       </c>
-      <c r="J19" s="216">
+      <c r="J19" s="213">
         <v>3.35</v>
       </c>
-      <c r="K19" s="211">
+      <c r="K19" s="219">
         <v>2.78</v>
       </c>
-      <c r="L19" s="219">
+      <c r="L19" s="214">
         <v>3.08</v>
       </c>
-      <c r="M19" s="213">
+      <c r="M19" s="208">
         <v>5.09</v>
       </c>
-      <c r="N19" s="208">
+      <c r="N19" s="215">
         <v>4.08</v>
       </c>
       <c r="O19" s="209">
         <v>5.66</v>
       </c>
-      <c r="P19" s="214">
+      <c r="P19" s="217">
         <v>9.79</v>
       </c>
-      <c r="Q19" s="217">
+      <c r="Q19" s="210">
         <v>11.41</v>
       </c>
-      <c r="R19" s="218">
+      <c r="R19" s="211">
         <v>13.65</v>
       </c>
-      <c r="S19" s="215">
+      <c r="S19" s="212">
         <v>17.55</v>
       </c>
-      <c r="T19" s="210">
+      <c r="T19" s="218">
         <v>1.86</v>
       </c>
     </row>

--- a/youzi/落升(江南神鹰)/index.xlsx
+++ b/youzi/落升(江南神鹰)/index.xlsx
@@ -39,6 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBC2635"/>
         <bgColor/>
       </patternFill>
@@ -51,73 +117,463 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCEAD3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,1225 +585,769 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF84CC94"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4352"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC72B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3898,7 +3898,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="8" t="str">
+      <c r="D2" s="11" t="str">
         <v>净买: 1815.37万</v>
       </c>
       <c r="E2">
@@ -3913,40 +3913,40 @@
       <c r="H2">
         <v>10.02</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="5">
         <v>0</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="6">
         <v>2.04</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="2">
         <v>4.88</v>
       </c>
-      <c r="L2" s="13">
+      <c r="L2" s="7">
         <v>7.07</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="12">
         <v>7.94</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="13">
         <v>10.06</v>
       </c>
       <c r="O2" s="3">
         <v>21.06</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="9">
         <v>33.16</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="Q2" s="8">
         <v>23.03</v>
       </c>
-      <c r="R2" s="6">
+      <c r="R2" s="10">
         <v>25.8</v>
       </c>
-      <c r="S2" s="12">
+      <c r="S2" s="4">
         <v>24.05</v>
       </c>
-      <c r="T2" s="7">
+      <c r="T2" s="1">
         <v>-32</v>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       <c r="C3" t="str">
         <v>605588</v>
       </c>
-      <c r="D3" s="15" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 1980.32万</v>
       </c>
       <c r="E3">
@@ -3975,40 +3975,40 @@
       <c r="H3">
         <v>10.01</v>
       </c>
-      <c r="I3" s="24">
+      <c r="I3" s="22">
         <v>0</v>
       </c>
-      <c r="J3" s="16">
+      <c r="J3" s="18">
         <v>6.96</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="17">
         <v>6.11</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="19">
         <v>-2.38</v>
       </c>
       <c r="M3" s="26">
         <v>-10.29</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="20">
         <v>-19.26</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="21">
         <v>-18.34</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="14">
         <v>-18.05</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="23">
         <v>-17.13</v>
       </c>
-      <c r="R3" s="20">
+      <c r="R3" s="24">
         <v>-13.31</v>
       </c>
-      <c r="S3" s="21">
+      <c r="S3" s="15">
         <v>-13.66</v>
       </c>
-      <c r="T3" s="14">
+      <c r="T3" s="16">
         <v>4.46</v>
       </c>
     </row>
@@ -4022,7 +4022,7 @@
       <c r="C4" t="str">
         <v>002165</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="29" t="str">
         <v>净买: 3957.43万</v>
       </c>
       <c r="E4">
@@ -4037,40 +4037,40 @@
       <c r="H4">
         <v>-10.02</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="30">
         <v>22.26</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="35">
         <v>16.61</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="36">
         <v>28.28</v>
       </c>
       <c r="L4" s="39">
         <v>18.25</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="27">
         <v>30.11</v>
       </c>
-      <c r="N4" s="27">
+      <c r="N4" s="28">
         <v>29.56</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="31">
         <v>32.48</v>
       </c>
-      <c r="P4" s="36">
+      <c r="P4" s="37">
         <v>40.15</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="34">
         <v>48.54</v>
       </c>
-      <c r="R4" s="29">
+      <c r="R4" s="38">
         <v>63.32</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="32">
         <v>79.74</v>
       </c>
-      <c r="T4" s="31">
+      <c r="T4" s="33">
         <v>77.55</v>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       <c r="C5" t="str">
         <v>002165</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="50" t="str">
         <v>净卖: -4519.88万</v>
       </c>
       <c r="E5">
@@ -4099,40 +4099,40 @@
       <c r="H5">
         <v>-8.21</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="46">
         <v>3.9</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="41">
         <v>14.31</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="47">
         <v>5.37</v>
       </c>
-      <c r="L5" s="49">
+      <c r="L5" s="42">
         <v>15.93</v>
       </c>
-      <c r="M5" s="40">
+      <c r="M5" s="51">
         <v>15.45</v>
       </c>
-      <c r="N5" s="41">
+      <c r="N5" s="43">
         <v>18.05</v>
       </c>
-      <c r="O5" s="45">
+      <c r="O5" s="52">
         <v>24.88</v>
       </c>
-      <c r="P5" s="42">
+      <c r="P5" s="49">
         <v>32.36</v>
       </c>
-      <c r="Q5" s="46">
+      <c r="Q5" s="40">
         <v>45.53</v>
       </c>
-      <c r="R5" s="43">
+      <c r="R5" s="48">
         <v>60.16</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="44">
         <v>76.26</v>
       </c>
-      <c r="T5" s="44">
+      <c r="T5" s="45">
         <v>58.21</v>
       </c>
     </row>
@@ -4146,7 +4146,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="65" t="str">
+      <c r="D6" s="63" t="str">
         <v>净买: 1976.41万</v>
       </c>
       <c r="E6">
@@ -4161,37 +4161,37 @@
       <c r="H6">
         <v>10</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="64">
         <v>0</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="55">
         <v>9.93</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="58">
         <v>20.88</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="65">
         <v>33</v>
       </c>
-      <c r="M6" s="62">
+      <c r="M6" s="59">
         <v>43.1</v>
       </c>
-      <c r="N6" s="54">
+      <c r="N6" s="60">
         <v>28.79</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="56">
         <v>19.36</v>
       </c>
-      <c r="P6" s="55">
+      <c r="P6" s="53">
         <v>21.55</v>
       </c>
-      <c r="Q6" s="56">
+      <c r="Q6" s="61">
         <v>9.43</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="62">
         <v>4.04</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="54">
         <v>4.38</v>
       </c>
       <c r="T6" s="57">
@@ -4208,7 +4208,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="68" t="str">
+      <c r="D7" s="77" t="str">
         <v>净卖: -2117.52万</v>
       </c>
       <c r="E7">
@@ -4223,10 +4223,10 @@
       <c r="H7">
         <v>7.72</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="78">
         <v>2.15</v>
       </c>
-      <c r="J7" s="74">
+      <c r="J7" s="73">
         <v>1.72</v>
       </c>
       <c r="K7" s="69">
@@ -4235,28 +4235,28 @@
       <c r="L7" s="70">
         <v>10.03</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="71">
         <v>16.62</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="66">
         <v>28.22</v>
       </c>
-      <c r="O7" s="77">
+      <c r="O7" s="74">
         <v>41.12</v>
       </c>
       <c r="P7" s="75">
         <v>55.3</v>
       </c>
-      <c r="Q7" s="72">
+      <c r="Q7" s="67">
         <v>70.77</v>
       </c>
-      <c r="R7" s="76">
+      <c r="R7" s="72">
         <v>73.21</v>
       </c>
-      <c r="S7" s="78">
+      <c r="S7" s="76">
         <v>90.54</v>
       </c>
-      <c r="T7" s="73">
+      <c r="T7" s="68">
         <v>39.4</v>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       <c r="C8" t="str">
         <v>002923</v>
       </c>
-      <c r="D8" s="82" t="str">
+      <c r="D8" s="91" t="str">
         <v>净买: 1689.05万</v>
       </c>
       <c r="E8">
@@ -4285,40 +4285,40 @@
       <c r="H8">
         <v>-5.06</v>
       </c>
-      <c r="I8" s="88">
+      <c r="I8" s="86">
         <v>-5.2</v>
       </c>
       <c r="J8" s="79">
         <v>-2.53</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="80">
         <v>-6.53</v>
       </c>
       <c r="L8" s="87">
         <v>-6.07</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="81">
         <v>-4.07</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="82">
         <v>-13.67</v>
       </c>
-      <c r="O8" s="84">
+      <c r="O8" s="83">
         <v>-17</v>
       </c>
-      <c r="P8" s="85">
+      <c r="P8" s="84">
         <v>-19.33</v>
       </c>
-      <c r="Q8" s="90">
+      <c r="Q8" s="85">
         <v>-16</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="88">
         <v>-17.47</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="89">
         <v>-15</v>
       </c>
-      <c r="T8" s="91">
+      <c r="T8" s="90">
         <v>-16.27</v>
       </c>
     </row>
@@ -4332,7 +4332,7 @@
       <c r="C9" t="str">
         <v>000965</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="98" t="str">
         <v>净卖: -66.63万</v>
       </c>
       <c r="E9">
@@ -4347,40 +4347,40 @@
       <c r="H9">
         <v>0.31</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="101">
         <v>8.75</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="99">
         <v>-1.56</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="92">
         <v>-0.94</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="102">
         <v>-3.75</v>
       </c>
-      <c r="M9" s="97">
+      <c r="M9" s="103">
         <v>5.94</v>
       </c>
-      <c r="N9" s="101">
+      <c r="N9" s="93">
         <v>16.56</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="100">
         <v>28.12</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="104">
         <v>40.94</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="94">
         <v>55</v>
       </c>
-      <c r="R9" s="102">
+      <c r="R9" s="95">
         <v>48.12</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="97">
         <v>62.81</v>
       </c>
-      <c r="T9" s="95">
+      <c r="T9" s="96">
         <v>14.06</v>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       <c r="C10" t="str">
         <v>002981</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="113" t="str">
         <v>净买: 1574.45万</v>
       </c>
       <c r="E10">
@@ -4409,40 +4409,40 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="115">
+      <c r="I10" s="114">
         <v>-0.74</v>
       </c>
-      <c r="J10" s="116">
+      <c r="J10" s="115">
         <v>-10.6</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="107">
         <v>-14.1</v>
       </c>
       <c r="L10" s="117">
         <v>-12.78</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="108">
         <v>-4.07</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="112">
         <v>-3.06</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="109">
         <v>-6.09</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="116">
         <v>3.33</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="110">
         <v>-2.01</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="111">
         <v>-1.88</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="105">
         <v>-4.77</v>
       </c>
-      <c r="T10" s="114">
+      <c r="T10" s="106">
         <v>6.87</v>
       </c>
     </row>
@@ -4456,7 +4456,7 @@
       <c r="C11" t="str">
         <v>600794</v>
       </c>
-      <c r="D11" s="118" t="str">
+      <c r="D11" s="126" t="str">
         <v>净卖: -697.77万</v>
       </c>
       <c r="E11">
@@ -4471,40 +4471,40 @@
       <c r="H11">
         <v>-8.75</v>
       </c>
-      <c r="I11" s="127">
+      <c r="I11" s="118">
         <v>-1.46</v>
       </c>
-      <c r="J11" s="122">
+      <c r="J11" s="127">
         <v>-11.25</v>
       </c>
-      <c r="K11" s="123">
+      <c r="K11" s="119">
         <v>-17.08</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="122">
         <v>-14.37</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="120">
         <v>-11.67</v>
       </c>
-      <c r="N11" s="129">
+      <c r="N11" s="128">
         <v>-12.71</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="129">
         <v>-15.42</v>
       </c>
-      <c r="P11" s="120">
+      <c r="P11" s="123">
         <v>-15.42</v>
       </c>
       <c r="Q11" s="124">
         <v>-12.29</v>
       </c>
-      <c r="R11" s="125">
+      <c r="R11" s="121">
         <v>-3.54</v>
       </c>
       <c r="S11" s="130">
         <v>-0.83</v>
       </c>
-      <c r="T11" s="126">
+      <c r="T11" s="125">
         <v>-25</v>
       </c>
     </row>
@@ -4518,7 +4518,7 @@
       <c r="C12" t="str">
         <v>000627</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="136" t="str">
         <v>净买: 1535.97万</v>
       </c>
       <c r="E12">
@@ -4533,40 +4533,40 @@
       <c r="H12">
         <v>-9.87</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="131">
         <v>0</v>
       </c>
-      <c r="J12" s="142">
+      <c r="J12" s="132">
         <v>-5.11</v>
       </c>
-      <c r="K12" s="133">
+      <c r="K12" s="137">
         <v>-9.85</v>
       </c>
-      <c r="L12" s="139">
+      <c r="L12" s="138">
         <v>-14.23</v>
       </c>
-      <c r="M12" s="136">
+      <c r="M12" s="142">
         <v>-18.61</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="143">
         <v>-22.63</v>
       </c>
-      <c r="O12" s="134">
+      <c r="O12" s="140">
         <v>-26.64</v>
       </c>
-      <c r="P12" s="143">
+      <c r="P12" s="133">
         <v>-30.29</v>
       </c>
-      <c r="Q12" s="137">
+      <c r="Q12" s="134">
         <v>-33.94</v>
       </c>
-      <c r="R12" s="131">
+      <c r="R12" s="139">
         <v>-36.86</v>
       </c>
-      <c r="S12" s="132">
+      <c r="S12" s="141">
         <v>-36.86</v>
       </c>
-      <c r="T12" s="138">
+      <c r="T12" s="135">
         <v>-42.34</v>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="C13" t="str">
         <v>603669</v>
       </c>
-      <c r="D13" s="148" t="str">
+      <c r="D13" s="153" t="str">
         <v>净卖: -338.04万</v>
       </c>
       <c r="E13">
@@ -4595,40 +4595,40 @@
       <c r="H13">
         <v>0.7</v>
       </c>
-      <c r="I13" s="153">
+      <c r="I13" s="150">
         <v>9.25</v>
       </c>
-      <c r="J13" s="149">
+      <c r="J13" s="154">
         <v>9.77</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="146">
         <v>10.65</v>
       </c>
-      <c r="L13" s="154">
+      <c r="L13" s="155">
         <v>8.9</v>
       </c>
-      <c r="M13" s="155">
+      <c r="M13" s="156">
         <v>8.2</v>
       </c>
-      <c r="N13" s="151">
+      <c r="N13" s="147">
         <v>7.33</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="148">
         <v>4.36</v>
       </c>
-      <c r="P13" s="145">
+      <c r="P13" s="151">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="144">
+      <c r="Q13" s="145">
         <v>1.05</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="149">
         <v>4.71</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="144">
         <v>3.84</v>
       </c>
-      <c r="T13" s="147">
+      <c r="T13" s="152">
         <v>-22.69</v>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       <c r="C14" t="str">
         <v>000029</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="169" t="str">
         <v>净卖: -639.40万</v>
       </c>
       <c r="E14">
@@ -4657,40 +4657,40 @@
       <c r="H14">
         <v>-9.37</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="160">
         <v>-0.7</v>
       </c>
-      <c r="J14" s="162">
+      <c r="J14" s="165">
         <v>-3</v>
       </c>
       <c r="K14" s="157">
         <v>-4.4</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="161">
         <v>-2.57</v>
       </c>
       <c r="M14" s="163">
         <v>-6.27</v>
       </c>
-      <c r="N14" s="160">
+      <c r="N14" s="162">
         <v>-6.34</v>
       </c>
-      <c r="O14" s="165">
+      <c r="O14" s="166">
         <v>-10.14</v>
       </c>
-      <c r="P14" s="158">
+      <c r="P14" s="167">
         <v>-5.84</v>
       </c>
-      <c r="Q14" s="166">
+      <c r="Q14" s="168">
         <v>-7.84</v>
       </c>
-      <c r="R14" s="161">
+      <c r="R14" s="164">
         <v>-9.34</v>
       </c>
-      <c r="S14" s="164">
+      <c r="S14" s="158">
         <v>-8.27</v>
       </c>
-      <c r="T14" s="167">
+      <c r="T14" s="159">
         <v>-32.05</v>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       <c r="C15" t="str">
         <v>002856</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="175" t="str">
         <v>净买: 611.16万</v>
       </c>
       <c r="E15">
@@ -4719,31 +4719,31 @@
       <c r="H15">
         <v>-6.28</v>
       </c>
-      <c r="I15" s="178">
+      <c r="I15" s="176">
         <v>17.36</v>
       </c>
-      <c r="J15" s="170">
+      <c r="J15" s="179">
         <v>12.95</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="177">
         <v>15.42</v>
       </c>
-      <c r="L15" s="172">
+      <c r="L15" s="178">
         <v>15.86</v>
       </c>
-      <c r="M15" s="173">
+      <c r="M15" s="170">
         <v>13.22</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="171">
         <v>9.87</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="172">
         <v>15.95</v>
       </c>
-      <c r="P15" s="176">
+      <c r="P15" s="180">
         <v>16.56</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="173">
         <v>14.8</v>
       </c>
       <c r="R15" s="181">
@@ -4752,7 +4752,7 @@
       <c r="S15" s="174">
         <v>5.55</v>
       </c>
-      <c r="T15" s="177">
+      <c r="T15" s="182">
         <v>1.76</v>
       </c>
     </row>
@@ -4766,7 +4766,7 @@
       <c r="C16" t="str">
         <v>603017</v>
       </c>
-      <c r="D16" s="195" t="str">
+      <c r="D16" s="185" t="str">
         <v>净买: 1022.95万</v>
       </c>
       <c r="E16">
@@ -4781,37 +4781,37 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="183">
+      <c r="I16" s="194">
         <v>0</v>
       </c>
-      <c r="J16" s="191">
+      <c r="J16" s="195">
         <v>10</v>
       </c>
-      <c r="K16" s="187">
+      <c r="K16" s="191">
         <v>-0.98</v>
       </c>
-      <c r="L16" s="188">
+      <c r="L16" s="192">
         <v>-6.69</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="183">
         <v>-9.32</v>
       </c>
-      <c r="N16" s="185">
+      <c r="N16" s="188">
         <v>-9.55</v>
       </c>
-      <c r="O16" s="192">
+      <c r="O16" s="193">
         <v>-8.87</v>
       </c>
-      <c r="P16" s="193">
+      <c r="P16" s="189">
         <v>-9.25</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="184">
         <v>-7.74</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="186">
         <v>-3.68</v>
       </c>
-      <c r="S16" s="194">
+      <c r="S16" s="187">
         <v>-4.59</v>
       </c>
       <c r="T16" s="190">
@@ -4877,40 +4877,40 @@
       <c r="F18" t="str"/>
       <c r="G18" t="str"/>
       <c r="H18" t="str"/>
-      <c r="I18" s="196">
+      <c r="I18" s="206">
         <v>40</v>
       </c>
-      <c r="J18" s="205">
+      <c r="J18" s="207">
         <v>60</v>
       </c>
-      <c r="K18" s="202">
+      <c r="K18" s="198">
         <v>53.33</v>
       </c>
-      <c r="L18" s="206">
+      <c r="L18" s="199">
         <v>46.67</v>
       </c>
-      <c r="M18" s="197">
+      <c r="M18" s="200">
         <v>53.33</v>
       </c>
-      <c r="N18" s="201">
+      <c r="N18" s="203">
         <v>53.33</v>
       </c>
-      <c r="O18" s="198">
+      <c r="O18" s="204">
         <v>53.33</v>
       </c>
-      <c r="P18" s="199">
+      <c r="P18" s="196">
         <v>60</v>
       </c>
-      <c r="Q18" s="203">
+      <c r="Q18" s="201">
         <v>53.33</v>
       </c>
-      <c r="R18" s="207">
+      <c r="R18" s="197">
         <v>53.33</v>
       </c>
-      <c r="S18" s="200">
+      <c r="S18" s="205">
         <v>53.33</v>
       </c>
-      <c r="T18" s="204">
+      <c r="T18" s="202">
         <v>46.67</v>
       </c>
     </row>
@@ -4925,40 +4925,40 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="216">
+      <c r="I19" s="213">
         <v>3.7</v>
       </c>
-      <c r="J19" s="213">
+      <c r="J19" s="214">
         <v>3.35</v>
       </c>
-      <c r="K19" s="219">
+      <c r="K19" s="215">
         <v>2.78</v>
       </c>
-      <c r="L19" s="214">
+      <c r="L19" s="210">
         <v>3.08</v>
       </c>
-      <c r="M19" s="208">
+      <c r="M19" s="216">
         <v>5.09</v>
       </c>
-      <c r="N19" s="215">
+      <c r="N19" s="217">
         <v>4.08</v>
       </c>
-      <c r="O19" s="209">
+      <c r="O19" s="219">
         <v>5.66</v>
       </c>
-      <c r="P19" s="217">
+      <c r="P19" s="208">
         <v>9.79</v>
       </c>
-      <c r="Q19" s="210">
+      <c r="Q19" s="209">
         <v>11.41</v>
       </c>
-      <c r="R19" s="211">
+      <c r="R19" s="218">
         <v>13.65</v>
       </c>
-      <c r="S19" s="212">
+      <c r="S19" s="211">
         <v>17.55</v>
       </c>
-      <c r="T19" s="218">
+      <c r="T19" s="212">
         <v>1.86</v>
       </c>
     </row>

--- a/youzi/落升(江南神鹰)/index.xlsx
+++ b/youzi/落升(江南神鹰)/index.xlsx
@@ -39,19 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3949"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -69,31 +123,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46773"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,13 +171,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC72B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,13 +189,1117 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6E1C0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25764"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -147,1135 +1311,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF98D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCCEAD3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF84CC94"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1294,48 +1336,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4352"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3916,38 +3916,38 @@
       <c r="I2" s="5">
         <v>0</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="2">
         <v>2.04</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="6">
         <v>4.88</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="12">
         <v>7.07</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="7">
         <v>7.94</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="8">
         <v>10.06</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="13">
         <v>21.06</v>
       </c>
       <c r="P2" s="9">
         <v>33.16</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="3">
         <v>23.03</v>
       </c>
       <c r="R2" s="10">
         <v>25.8</v>
       </c>
-      <c r="S2" s="4">
+      <c r="S2" s="1">
         <v>24.05</v>
       </c>
-      <c r="T2" s="1">
-        <v>-32</v>
+      <c r="T2" s="4">
+        <v>-32.22</v>
       </c>
     </row>
     <row r="3">
@@ -3960,7 +3960,7 @@
       <c r="C3" t="str">
         <v>605588</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="22" t="str">
         <v>净买: 1980.32万</v>
       </c>
       <c r="E3">
@@ -3975,19 +3975,19 @@
       <c r="H3">
         <v>10.01</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="14">
         <v>0</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="23">
         <v>6.96</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="15">
         <v>6.11</v>
       </c>
-      <c r="L3" s="19">
+      <c r="L3" s="16">
         <v>-2.38</v>
       </c>
-      <c r="M3" s="26">
+      <c r="M3" s="19">
         <v>-10.29</v>
       </c>
       <c r="N3" s="20">
@@ -3996,20 +3996,20 @@
       <c r="O3" s="21">
         <v>-18.34</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="24">
         <v>-18.05</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="25">
         <v>-17.13</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="17">
         <v>-13.31</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="26">
         <v>-13.66</v>
       </c>
-      <c r="T3" s="16">
-        <v>4.46</v>
+      <c r="T3" s="18">
+        <v>3.74</v>
       </c>
     </row>
     <row r="4">
@@ -4022,7 +4022,7 @@
       <c r="C4" t="str">
         <v>002165</v>
       </c>
-      <c r="D4" s="29" t="str">
+      <c r="D4" s="30" t="str">
         <v>净买: 3957.43万</v>
       </c>
       <c r="E4">
@@ -4037,41 +4037,41 @@
       <c r="H4">
         <v>-10.02</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="34">
         <v>22.26</v>
       </c>
       <c r="J4" s="35">
         <v>16.61</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="31">
         <v>28.28</v>
       </c>
-      <c r="L4" s="39">
+      <c r="L4" s="36">
         <v>18.25</v>
       </c>
       <c r="M4" s="27">
         <v>30.11</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="29">
         <v>29.56</v>
       </c>
-      <c r="O4" s="31">
+      <c r="O4" s="32">
         <v>32.48</v>
       </c>
       <c r="P4" s="37">
         <v>40.15</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="28">
         <v>48.54</v>
       </c>
       <c r="R4" s="38">
         <v>63.32</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="39">
         <v>79.74</v>
       </c>
       <c r="T4" s="33">
-        <v>77.55</v>
+        <v>78.47</v>
       </c>
     </row>
     <row r="5">
@@ -4084,7 +4084,7 @@
       <c r="C5" t="str">
         <v>002165</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="52" t="str">
         <v>净卖: -4519.88万</v>
       </c>
       <c r="E5">
@@ -4099,41 +4099,41 @@
       <c r="H5">
         <v>-8.21</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="41">
         <v>3.9</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="44">
         <v>14.31</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="48">
         <v>5.37</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="40">
         <v>15.93</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="42">
         <v>15.45</v>
       </c>
-      <c r="N5" s="43">
+      <c r="N5" s="45">
         <v>18.05</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="46">
         <v>24.88</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="43">
         <v>32.36</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="49">
         <v>45.53</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="50">
         <v>60.16</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="51">
         <v>76.26</v>
       </c>
-      <c r="T5" s="45">
-        <v>58.21</v>
+      <c r="T5" s="47">
+        <v>59.02</v>
       </c>
     </row>
     <row r="6">
@@ -4146,7 +4146,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="63" t="str">
+      <c r="D6" s="53" t="str">
         <v>净买: 1976.41万</v>
       </c>
       <c r="E6">
@@ -4161,41 +4161,41 @@
       <c r="H6">
         <v>10</v>
       </c>
-      <c r="I6" s="64">
+      <c r="I6" s="63">
         <v>0</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="54">
         <v>9.93</v>
       </c>
-      <c r="K6" s="58">
+      <c r="K6" s="60">
         <v>20.88</v>
       </c>
-      <c r="L6" s="65">
+      <c r="L6" s="56">
         <v>33</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="64">
         <v>43.1</v>
       </c>
-      <c r="N6" s="60">
+      <c r="N6" s="57">
         <v>28.79</v>
       </c>
-      <c r="O6" s="56">
+      <c r="O6" s="58">
         <v>19.36</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="61">
         <v>21.55</v>
       </c>
-      <c r="Q6" s="61">
+      <c r="Q6" s="65">
         <v>9.43</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="59">
         <v>4.04</v>
       </c>
-      <c r="S6" s="54">
+      <c r="S6" s="62">
         <v>4.38</v>
       </c>
-      <c r="T6" s="57">
-        <v>-1.18</v>
+      <c r="T6" s="55">
+        <v>-1.68</v>
       </c>
     </row>
     <row r="7">
@@ -4208,7 +4208,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="77" t="str">
+      <c r="D7" s="67" t="str">
         <v>净卖: -2117.52万</v>
       </c>
       <c r="E7">
@@ -4223,41 +4223,41 @@
       <c r="H7">
         <v>7.72</v>
       </c>
-      <c r="I7" s="78">
+      <c r="I7" s="77">
         <v>2.15</v>
       </c>
-      <c r="J7" s="73">
+      <c r="J7" s="78">
         <v>1.72</v>
       </c>
-      <c r="K7" s="69">
+      <c r="K7" s="66">
         <v>4.01</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="73">
         <v>10.03</v>
       </c>
-      <c r="M7" s="71">
+      <c r="M7" s="68">
         <v>16.62</v>
       </c>
-      <c r="N7" s="66">
+      <c r="N7" s="74">
         <v>28.22</v>
       </c>
-      <c r="O7" s="74">
+      <c r="O7" s="69">
         <v>41.12</v>
       </c>
-      <c r="P7" s="75">
+      <c r="P7" s="72">
         <v>55.3</v>
       </c>
-      <c r="Q7" s="67">
+      <c r="Q7" s="70">
         <v>70.77</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="75">
         <v>73.21</v>
       </c>
       <c r="S7" s="76">
         <v>90.54</v>
       </c>
-      <c r="T7" s="68">
-        <v>39.4</v>
+      <c r="T7" s="71">
+        <v>40.11</v>
       </c>
     </row>
     <row r="8">
@@ -4270,7 +4270,7 @@
       <c r="C8" t="str">
         <v>002923</v>
       </c>
-      <c r="D8" s="91" t="str">
+      <c r="D8" s="86" t="str">
         <v>净买: 1689.05万</v>
       </c>
       <c r="E8">
@@ -4285,41 +4285,41 @@
       <c r="H8">
         <v>-5.06</v>
       </c>
-      <c r="I8" s="86">
+      <c r="I8" s="87">
         <v>-5.2</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="91">
         <v>-2.53</v>
       </c>
-      <c r="K8" s="80">
+      <c r="K8" s="79">
         <v>-6.53</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="88">
         <v>-6.07</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="89">
         <v>-4.07</v>
       </c>
-      <c r="N8" s="82">
+      <c r="N8" s="80">
         <v>-13.67</v>
       </c>
-      <c r="O8" s="83">
+      <c r="O8" s="81">
         <v>-17</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="90">
         <v>-19.33</v>
       </c>
-      <c r="Q8" s="85">
+      <c r="Q8" s="84">
         <v>-16</v>
       </c>
-      <c r="R8" s="88">
+      <c r="R8" s="85">
         <v>-17.47</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="82">
         <v>-15</v>
       </c>
-      <c r="T8" s="90">
-        <v>-16.27</v>
+      <c r="T8" s="83">
+        <v>-16.67</v>
       </c>
     </row>
     <row r="9">
@@ -4332,7 +4332,7 @@
       <c r="C9" t="str">
         <v>000965</v>
       </c>
-      <c r="D9" s="98" t="str">
+      <c r="D9" s="92" t="str">
         <v>净卖: -66.63万</v>
       </c>
       <c r="E9">
@@ -4350,38 +4350,38 @@
       <c r="I9" s="101">
         <v>8.75</v>
       </c>
-      <c r="J9" s="99">
+      <c r="J9" s="103">
         <v>-1.56</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="97">
         <v>-0.94</v>
       </c>
-      <c r="L9" s="102">
+      <c r="L9" s="93">
         <v>-3.75</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="94">
         <v>5.94</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="98">
         <v>16.56</v>
       </c>
-      <c r="O9" s="100">
+      <c r="O9" s="99">
         <v>28.12</v>
       </c>
-      <c r="P9" s="104">
+      <c r="P9" s="95">
         <v>40.94</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="102">
         <v>55</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="100">
         <v>48.12</v>
       </c>
-      <c r="S9" s="97">
+      <c r="S9" s="96">
         <v>62.81</v>
       </c>
-      <c r="T9" s="96">
-        <v>14.06</v>
+      <c r="T9" s="104">
+        <v>13.44</v>
       </c>
     </row>
     <row r="10">
@@ -4394,7 +4394,7 @@
       <c r="C10" t="str">
         <v>002981</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="106" t="str">
         <v>净买: 1574.45万</v>
       </c>
       <c r="E10">
@@ -4409,41 +4409,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="114">
+      <c r="I10" s="113">
         <v>-0.74</v>
       </c>
-      <c r="J10" s="115">
+      <c r="J10" s="114">
         <v>-10.6</v>
       </c>
-      <c r="K10" s="107">
+      <c r="K10" s="115">
         <v>-14.1</v>
       </c>
-      <c r="L10" s="117">
+      <c r="L10" s="116">
         <v>-12.78</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="117">
         <v>-4.07</v>
       </c>
-      <c r="N10" s="112">
+      <c r="N10" s="107">
         <v>-3.06</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="112">
         <v>-6.09</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="108">
         <v>3.33</v>
       </c>
-      <c r="Q10" s="110">
+      <c r="Q10" s="109">
         <v>-2.01</v>
       </c>
-      <c r="R10" s="111">
+      <c r="R10" s="105">
         <v>-1.88</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="110">
         <v>-4.77</v>
       </c>
-      <c r="T10" s="106">
-        <v>6.87</v>
+      <c r="T10" s="111">
+        <v>8.58</v>
       </c>
     </row>
     <row r="11">
@@ -4471,40 +4471,40 @@
       <c r="H11">
         <v>-8.75</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="130">
         <v>-1.46</v>
       </c>
       <c r="J11" s="127">
         <v>-11.25</v>
       </c>
-      <c r="K11" s="119">
+      <c r="K11" s="128">
         <v>-17.08</v>
       </c>
-      <c r="L11" s="122">
+      <c r="L11" s="118">
         <v>-14.37</v>
       </c>
       <c r="M11" s="120">
         <v>-11.67</v>
       </c>
-      <c r="N11" s="128">
+      <c r="N11" s="121">
         <v>-12.71</v>
       </c>
-      <c r="O11" s="129">
+      <c r="O11" s="122">
         <v>-15.42</v>
       </c>
-      <c r="P11" s="123">
+      <c r="P11" s="129">
         <v>-15.42</v>
       </c>
-      <c r="Q11" s="124">
+      <c r="Q11" s="119">
         <v>-12.29</v>
       </c>
-      <c r="R11" s="121">
+      <c r="R11" s="123">
         <v>-3.54</v>
       </c>
-      <c r="S11" s="130">
+      <c r="S11" s="125">
         <v>-0.83</v>
       </c>
-      <c r="T11" s="125">
+      <c r="T11" s="124">
         <v>-25</v>
       </c>
     </row>
@@ -4533,37 +4533,37 @@
       <c r="H12">
         <v>-9.87</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="137">
         <v>0</v>
       </c>
-      <c r="J12" s="132">
+      <c r="J12" s="139">
         <v>-5.11</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="138">
         <v>-9.85</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="141">
         <v>-14.23</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="131">
         <v>-18.61</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="140">
         <v>-22.63</v>
       </c>
-      <c r="O12" s="140">
+      <c r="O12" s="142">
         <v>-26.64</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="132">
         <v>-30.29</v>
       </c>
-      <c r="Q12" s="134">
+      <c r="Q12" s="133">
         <v>-33.94</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="134">
         <v>-36.86</v>
       </c>
-      <c r="S12" s="141">
+      <c r="S12" s="143">
         <v>-36.86</v>
       </c>
       <c r="T12" s="135">
@@ -4580,7 +4580,7 @@
       <c r="C13" t="str">
         <v>603669</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -338.04万</v>
       </c>
       <c r="E13">
@@ -4595,41 +4595,41 @@
       <c r="H13">
         <v>0.7</v>
       </c>
-      <c r="I13" s="150">
+      <c r="I13" s="146">
         <v>9.25</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="152">
         <v>9.77</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="147">
         <v>10.65</v>
       </c>
-      <c r="L13" s="155">
+      <c r="L13" s="156">
         <v>8.9</v>
       </c>
-      <c r="M13" s="156">
+      <c r="M13" s="148">
         <v>8.2</v>
       </c>
-      <c r="N13" s="147">
+      <c r="N13" s="150">
         <v>7.33</v>
       </c>
-      <c r="O13" s="148">
+      <c r="O13" s="153">
         <v>4.36</v>
       </c>
-      <c r="P13" s="151">
+      <c r="P13" s="154">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="149">
         <v>1.05</v>
       </c>
-      <c r="R13" s="149">
+      <c r="R13" s="144">
         <v>4.71</v>
       </c>
-      <c r="S13" s="144">
+      <c r="S13" s="155">
         <v>3.84</v>
       </c>
-      <c r="T13" s="152">
-        <v>-22.69</v>
+      <c r="T13" s="151">
+        <v>-21.99</v>
       </c>
     </row>
     <row r="14">
@@ -4642,7 +4642,7 @@
       <c r="C14" t="str">
         <v>000029</v>
       </c>
-      <c r="D14" s="169" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -639.40万</v>
       </c>
       <c r="E14">
@@ -4657,41 +4657,41 @@
       <c r="H14">
         <v>-9.37</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="163">
         <v>-0.7</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="159">
         <v>-3</v>
       </c>
-      <c r="K14" s="157">
+      <c r="K14" s="164">
         <v>-4.4</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="165">
         <v>-2.57</v>
       </c>
-      <c r="M14" s="163">
+      <c r="M14" s="160">
         <v>-6.27</v>
       </c>
-      <c r="N14" s="162">
+      <c r="N14" s="161">
         <v>-6.34</v>
       </c>
-      <c r="O14" s="166">
+      <c r="O14" s="167">
         <v>-10.14</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="168">
         <v>-5.84</v>
       </c>
-      <c r="Q14" s="168">
+      <c r="Q14" s="169">
         <v>-7.84</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="162">
         <v>-9.34</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="166">
         <v>-8.27</v>
       </c>
-      <c r="T14" s="159">
-        <v>-32.05</v>
+      <c r="T14" s="157">
+        <v>-33.42</v>
       </c>
     </row>
     <row r="15">
@@ -4704,7 +4704,7 @@
       <c r="C15" t="str">
         <v>002856</v>
       </c>
-      <c r="D15" s="175" t="str">
+      <c r="D15" s="176" t="str">
         <v>净买: 611.16万</v>
       </c>
       <c r="E15">
@@ -4719,41 +4719,41 @@
       <c r="H15">
         <v>-6.28</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="177">
         <v>17.36</v>
       </c>
-      <c r="J15" s="179">
+      <c r="J15" s="180">
         <v>12.95</v>
       </c>
-      <c r="K15" s="177">
+      <c r="K15" s="178">
         <v>15.42</v>
       </c>
-      <c r="L15" s="178">
+      <c r="L15" s="179">
         <v>15.86</v>
       </c>
-      <c r="M15" s="170">
+      <c r="M15" s="171">
         <v>13.22</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="172">
         <v>9.87</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="173">
         <v>15.95</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="181">
         <v>16.56</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="174">
         <v>14.8</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="175">
         <v>11.45</v>
       </c>
-      <c r="S15" s="174">
+      <c r="S15" s="182">
         <v>5.55</v>
       </c>
-      <c r="T15" s="182">
-        <v>1.76</v>
+      <c r="T15" s="170">
+        <v>4.14</v>
       </c>
     </row>
     <row r="16">
@@ -4784,38 +4784,38 @@
       <c r="I16" s="194">
         <v>0</v>
       </c>
-      <c r="J16" s="195">
+      <c r="J16" s="190">
         <v>10</v>
       </c>
-      <c r="K16" s="191">
+      <c r="K16" s="183">
         <v>-0.98</v>
       </c>
-      <c r="L16" s="192">
+      <c r="L16" s="186">
         <v>-6.69</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="187">
         <v>-9.32</v>
       </c>
-      <c r="N16" s="188">
+      <c r="N16" s="195">
         <v>-9.55</v>
       </c>
-      <c r="O16" s="193">
+      <c r="O16" s="184">
         <v>-8.87</v>
       </c>
-      <c r="P16" s="189">
+      <c r="P16" s="191">
         <v>-9.25</v>
       </c>
-      <c r="Q16" s="184">
+      <c r="Q16" s="188">
         <v>-7.74</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="189">
         <v>-3.68</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="192">
         <v>-4.59</v>
       </c>
-      <c r="T16" s="190">
-        <v>-2.86</v>
+      <c r="T16" s="193">
+        <v>6.84</v>
       </c>
     </row>
     <row r="17">
@@ -4877,41 +4877,41 @@
       <c r="F18" t="str"/>
       <c r="G18" t="str"/>
       <c r="H18" t="str"/>
-      <c r="I18" s="206">
+      <c r="I18" s="202">
         <v>40</v>
       </c>
-      <c r="J18" s="207">
+      <c r="J18" s="203">
         <v>60</v>
       </c>
-      <c r="K18" s="198">
+      <c r="K18" s="207">
         <v>53.33</v>
       </c>
-      <c r="L18" s="199">
+      <c r="L18" s="206">
         <v>46.67</v>
       </c>
-      <c r="M18" s="200">
+      <c r="M18" s="198">
         <v>53.33</v>
       </c>
-      <c r="N18" s="203">
+      <c r="N18" s="199">
         <v>53.33</v>
       </c>
-      <c r="O18" s="204">
+      <c r="O18" s="196">
         <v>53.33</v>
       </c>
-      <c r="P18" s="196">
+      <c r="P18" s="200">
         <v>60</v>
       </c>
-      <c r="Q18" s="201">
+      <c r="Q18" s="204">
         <v>53.33</v>
       </c>
-      <c r="R18" s="197">
+      <c r="R18" s="205">
         <v>53.33</v>
       </c>
-      <c r="S18" s="205">
+      <c r="S18" s="201">
         <v>53.33</v>
       </c>
-      <c r="T18" s="202">
-        <v>46.67</v>
+      <c r="T18" s="197">
+        <v>53.33</v>
       </c>
     </row>
     <row r="19">
@@ -4925,41 +4925,41 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="213">
+      <c r="I19" s="209">
         <v>3.7</v>
       </c>
       <c r="J19" s="214">
         <v>3.35</v>
       </c>
-      <c r="K19" s="215">
+      <c r="K19" s="212">
         <v>2.78</v>
       </c>
-      <c r="L19" s="210">
+      <c r="L19" s="217">
         <v>3.08</v>
       </c>
-      <c r="M19" s="216">
+      <c r="M19" s="218">
         <v>5.09</v>
       </c>
-      <c r="N19" s="217">
+      <c r="N19" s="215">
         <v>4.08</v>
       </c>
-      <c r="O19" s="219">
+      <c r="O19" s="213">
         <v>5.66</v>
       </c>
-      <c r="P19" s="208">
+      <c r="P19" s="210">
         <v>9.79</v>
       </c>
-      <c r="Q19" s="209">
+      <c r="Q19" s="219">
         <v>11.41</v>
       </c>
-      <c r="R19" s="218">
+      <c r="R19" s="208">
         <v>13.65</v>
       </c>
-      <c r="S19" s="211">
+      <c r="S19" s="216">
         <v>17.55</v>
       </c>
-      <c r="T19" s="212">
-        <v>1.86</v>
+      <c r="T19" s="211">
+        <v>2.73</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/落升(江南神鹰)/index.xlsx
+++ b/youzi/落升(江南神鹰)/index.xlsx
@@ -39,7 +39,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -51,7 +117,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -63,19 +135,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,13 +231,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8BCF9A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,13 +411,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D5A6"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,12 +531,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE46773"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -159,18 +543,126 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC72B3A"/>
         <bgColor/>
       </patternFill>
@@ -189,25 +681,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -219,127 +849,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -351,6 +975,150 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
@@ -363,49 +1131,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6E1C0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -417,19 +1197,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -441,109 +1239,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -555,355 +1263,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -915,277 +1317,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25764"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1197,151 +1341,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3898,7 +3898,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="12" t="str">
         <v>净买: 1815.37万</v>
       </c>
       <c r="E2">
@@ -3913,41 +3913,41 @@
       <c r="H2">
         <v>10.02</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="9">
         <v>0</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="13">
         <v>2.04</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>4.88</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="1">
         <v>7.07</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="2">
         <v>7.94</v>
       </c>
-      <c r="N2" s="8">
+      <c r="N2" s="5">
         <v>10.06</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="6">
         <v>21.06</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="7">
         <v>33.16</v>
       </c>
       <c r="Q2" s="3">
         <v>23.03</v>
       </c>
-      <c r="R2" s="10">
+      <c r="R2" s="8">
         <v>25.8</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="10">
         <v>24.05</v>
       </c>
-      <c r="T2" s="4">
-        <v>-32.22</v>
+      <c r="T2" s="11">
+        <v>-34.18</v>
       </c>
     </row>
     <row r="3">
@@ -3960,7 +3960,7 @@
       <c r="C3" t="str">
         <v>605588</v>
       </c>
-      <c r="D3" s="22" t="str">
+      <c r="D3" s="25" t="str">
         <v>净买: 1980.32万</v>
       </c>
       <c r="E3">
@@ -3975,41 +3975,41 @@
       <c r="H3">
         <v>10.01</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="26">
         <v>0</v>
       </c>
-      <c r="J3" s="23">
+      <c r="J3" s="14">
         <v>6.96</v>
       </c>
       <c r="K3" s="15">
         <v>6.11</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="23">
         <v>-2.38</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="18">
         <v>-10.29</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="16">
         <v>-19.26</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="20">
         <v>-18.34</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="17">
         <v>-18.05</v>
       </c>
-      <c r="Q3" s="25">
+      <c r="Q3" s="21">
         <v>-17.13</v>
       </c>
-      <c r="R3" s="17">
+      <c r="R3" s="24">
         <v>-13.31</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="19">
         <v>-13.66</v>
       </c>
-      <c r="T3" s="18">
-        <v>3.74</v>
+      <c r="T3" s="22">
+        <v>4.97</v>
       </c>
     </row>
     <row r="4">
@@ -4022,7 +4022,7 @@
       <c r="C4" t="str">
         <v>002165</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 3957.43万</v>
       </c>
       <c r="E4">
@@ -4037,41 +4037,41 @@
       <c r="H4">
         <v>-10.02</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="39">
         <v>22.26</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="36">
         <v>16.61</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="29">
         <v>28.28</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="33">
         <v>18.25</v>
       </c>
       <c r="M4" s="27">
         <v>30.11</v>
       </c>
-      <c r="N4" s="29">
+      <c r="N4" s="34">
         <v>29.56</v>
       </c>
-      <c r="O4" s="32">
+      <c r="O4" s="28">
         <v>32.48</v>
       </c>
-      <c r="P4" s="37">
+      <c r="P4" s="35">
         <v>40.15</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="30">
         <v>48.54</v>
       </c>
-      <c r="R4" s="38">
+      <c r="R4" s="37">
         <v>63.32</v>
       </c>
-      <c r="S4" s="39">
+      <c r="S4" s="38">
         <v>79.74</v>
       </c>
-      <c r="T4" s="33">
-        <v>78.47</v>
+      <c r="T4" s="31">
+        <v>74.82</v>
       </c>
     </row>
     <row r="5">
@@ -4084,7 +4084,7 @@
       <c r="C5" t="str">
         <v>002165</v>
       </c>
-      <c r="D5" s="52" t="str">
+      <c r="D5" s="51" t="str">
         <v>净卖: -4519.88万</v>
       </c>
       <c r="E5">
@@ -4099,41 +4099,41 @@
       <c r="H5">
         <v>-8.21</v>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="52">
         <v>3.9</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="45">
         <v>14.31</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="46">
         <v>5.37</v>
       </c>
       <c r="L5" s="40">
         <v>15.93</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="41">
         <v>15.45</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="42">
         <v>18.05</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="43">
         <v>24.88</v>
       </c>
-      <c r="P5" s="43">
+      <c r="P5" s="47">
         <v>32.36</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="48">
         <v>45.53</v>
       </c>
-      <c r="R5" s="50">
+      <c r="R5" s="49">
         <v>60.16</v>
       </c>
-      <c r="S5" s="51">
+      <c r="S5" s="50">
         <v>76.26</v>
       </c>
-      <c r="T5" s="47">
-        <v>59.02</v>
+      <c r="T5" s="44">
+        <v>55.77</v>
       </c>
     </row>
     <row r="6">
@@ -4146,7 +4146,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 1976.41万</v>
       </c>
       <c r="E6">
@@ -4161,41 +4161,41 @@
       <c r="H6">
         <v>10</v>
       </c>
-      <c r="I6" s="63">
+      <c r="I6" s="62">
         <v>0</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="59">
         <v>9.93</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="57">
         <v>20.88</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="63">
         <v>33</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="58">
         <v>43.1</v>
       </c>
-      <c r="N6" s="57">
+      <c r="N6" s="64">
         <v>28.79</v>
       </c>
-      <c r="O6" s="58">
+      <c r="O6" s="65">
         <v>19.36</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="53">
         <v>21.55</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="60">
         <v>9.43</v>
       </c>
-      <c r="R6" s="59">
+      <c r="R6" s="54">
         <v>4.04</v>
       </c>
-      <c r="S6" s="62">
+      <c r="S6" s="55">
         <v>4.38</v>
       </c>
-      <c r="T6" s="55">
-        <v>-1.68</v>
+      <c r="T6" s="61">
+        <v>-2.69</v>
       </c>
     </row>
     <row r="7">
@@ -4208,7 +4208,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="67" t="str">
+      <c r="D7" s="66" t="str">
         <v>净卖: -2117.52万</v>
       </c>
       <c r="E7">
@@ -4223,41 +4223,41 @@
       <c r="H7">
         <v>7.72</v>
       </c>
-      <c r="I7" s="77">
+      <c r="I7" s="67">
         <v>2.15</v>
       </c>
-      <c r="J7" s="78">
+      <c r="J7" s="70">
         <v>1.72</v>
       </c>
-      <c r="K7" s="66">
+      <c r="K7" s="76">
         <v>4.01</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="68">
         <v>10.03</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="77">
         <v>16.62</v>
       </c>
       <c r="N7" s="74">
         <v>28.22</v>
       </c>
-      <c r="O7" s="69">
+      <c r="O7" s="78">
         <v>41.12</v>
       </c>
-      <c r="P7" s="72">
+      <c r="P7" s="71">
         <v>55.3</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="75">
         <v>70.77</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="72">
         <v>73.21</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="69">
         <v>90.54</v>
       </c>
-      <c r="T7" s="71">
-        <v>40.11</v>
+      <c r="T7" s="73">
+        <v>37.25</v>
       </c>
     </row>
     <row r="8">
@@ -4270,7 +4270,7 @@
       <c r="C8" t="str">
         <v>002923</v>
       </c>
-      <c r="D8" s="86" t="str">
+      <c r="D8" s="88" t="str">
         <v>净买: 1689.05万</v>
       </c>
       <c r="E8">
@@ -4288,38 +4288,38 @@
       <c r="I8" s="87">
         <v>-5.2</v>
       </c>
-      <c r="J8" s="91">
+      <c r="J8" s="79">
         <v>-2.53</v>
       </c>
-      <c r="K8" s="79">
+      <c r="K8" s="85">
         <v>-6.53</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="80">
         <v>-6.07</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="81">
         <v>-4.07</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="89">
         <v>-13.67</v>
       </c>
-      <c r="O8" s="81">
+      <c r="O8" s="82">
         <v>-17</v>
       </c>
-      <c r="P8" s="90">
+      <c r="P8" s="86">
         <v>-19.33</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="83">
         <v>-16</v>
       </c>
-      <c r="R8" s="85">
+      <c r="R8" s="90">
         <v>-17.47</v>
       </c>
-      <c r="S8" s="82">
+      <c r="S8" s="84">
         <v>-15</v>
       </c>
-      <c r="T8" s="83">
-        <v>-16.67</v>
+      <c r="T8" s="91">
+        <v>-18</v>
       </c>
     </row>
     <row r="9">
@@ -4332,7 +4332,7 @@
       <c r="C9" t="str">
         <v>000965</v>
       </c>
-      <c r="D9" s="92" t="str">
+      <c r="D9" s="93" t="str">
         <v>净卖: -66.63万</v>
       </c>
       <c r="E9">
@@ -4347,41 +4347,41 @@
       <c r="H9">
         <v>0.31</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="100">
         <v>8.75</v>
       </c>
-      <c r="J9" s="103">
+      <c r="J9" s="98">
         <v>-1.56</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="103">
         <v>-0.94</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="94">
         <v>-3.75</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="95">
         <v>5.94</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="104">
         <v>16.56</v>
       </c>
-      <c r="O9" s="99">
+      <c r="O9" s="96">
         <v>28.12</v>
       </c>
-      <c r="P9" s="95">
+      <c r="P9" s="101">
         <v>40.94</v>
       </c>
       <c r="Q9" s="102">
         <v>55</v>
       </c>
-      <c r="R9" s="100">
+      <c r="R9" s="97">
         <v>48.12</v>
       </c>
-      <c r="S9" s="96">
+      <c r="S9" s="99">
         <v>62.81</v>
       </c>
-      <c r="T9" s="104">
-        <v>13.44</v>
+      <c r="T9" s="92">
+        <v>12.81</v>
       </c>
     </row>
     <row r="10">
@@ -4394,7 +4394,7 @@
       <c r="C10" t="str">
         <v>002981</v>
       </c>
-      <c r="D10" s="106" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 1574.45万</v>
       </c>
       <c r="E10">
@@ -4409,41 +4409,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="113">
+      <c r="I10" s="111">
         <v>-0.74</v>
       </c>
-      <c r="J10" s="114">
+      <c r="J10" s="106">
         <v>-10.6</v>
       </c>
-      <c r="K10" s="115">
+      <c r="K10" s="112">
         <v>-14.1</v>
       </c>
-      <c r="L10" s="116">
+      <c r="L10" s="107">
         <v>-12.78</v>
       </c>
-      <c r="M10" s="117">
+      <c r="M10" s="108">
         <v>-4.07</v>
       </c>
-      <c r="N10" s="107">
+      <c r="N10" s="115">
         <v>-3.06</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="113">
         <v>-6.09</v>
       </c>
-      <c r="P10" s="108">
+      <c r="P10" s="116">
         <v>3.33</v>
       </c>
-      <c r="Q10" s="109">
+      <c r="Q10" s="114">
         <v>-2.01</v>
       </c>
-      <c r="R10" s="105">
+      <c r="R10" s="109">
         <v>-1.88</v>
       </c>
-      <c r="S10" s="110">
+      <c r="S10" s="117">
         <v>-4.77</v>
       </c>
-      <c r="T10" s="111">
-        <v>8.58</v>
+      <c r="T10" s="105">
+        <v>6.96</v>
       </c>
     </row>
     <row r="11">
@@ -4456,7 +4456,7 @@
       <c r="C11" t="str">
         <v>600794</v>
       </c>
-      <c r="D11" s="126" t="str">
+      <c r="D11" s="122" t="str">
         <v>净卖: -697.77万</v>
       </c>
       <c r="E11">
@@ -4471,41 +4471,41 @@
       <c r="H11">
         <v>-8.75</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="123">
         <v>-1.46</v>
       </c>
-      <c r="J11" s="127">
+      <c r="J11" s="124">
         <v>-11.25</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="127">
         <v>-17.08</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="120">
         <v>-14.37</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="125">
         <v>-11.67</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="129">
         <v>-12.71</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="130">
         <v>-15.42</v>
       </c>
-      <c r="P11" s="129">
+      <c r="P11" s="126">
         <v>-15.42</v>
       </c>
-      <c r="Q11" s="119">
+      <c r="Q11" s="118">
         <v>-12.29</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="119">
         <v>-3.54</v>
       </c>
-      <c r="S11" s="125">
+      <c r="S11" s="121">
         <v>-0.83</v>
       </c>
-      <c r="T11" s="124">
-        <v>-25</v>
+      <c r="T11" s="128">
+        <v>-25.62</v>
       </c>
     </row>
     <row r="12">
@@ -4518,7 +4518,7 @@
       <c r="C12" t="str">
         <v>000627</v>
       </c>
-      <c r="D12" s="136" t="str">
+      <c r="D12" s="135" t="str">
         <v>净买: 1535.97万</v>
       </c>
       <c r="E12">
@@ -4533,40 +4533,40 @@
       <c r="H12">
         <v>-9.87</v>
       </c>
-      <c r="I12" s="137">
+      <c r="I12" s="136">
         <v>0</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="133">
         <v>-5.11</v>
       </c>
-      <c r="K12" s="138">
+      <c r="K12" s="140">
         <v>-9.85</v>
       </c>
-      <c r="L12" s="141">
+      <c r="L12" s="142">
         <v>-14.23</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="143">
         <v>-18.61</v>
       </c>
-      <c r="N12" s="140">
+      <c r="N12" s="137">
         <v>-22.63</v>
       </c>
-      <c r="O12" s="142">
+      <c r="O12" s="131">
         <v>-26.64</v>
       </c>
       <c r="P12" s="132">
         <v>-30.29</v>
       </c>
-      <c r="Q12" s="133">
+      <c r="Q12" s="138">
         <v>-33.94</v>
       </c>
-      <c r="R12" s="134">
+      <c r="R12" s="139">
         <v>-36.86</v>
       </c>
-      <c r="S12" s="143">
+      <c r="S12" s="141">
         <v>-36.86</v>
       </c>
-      <c r="T12" s="135">
+      <c r="T12" s="134">
         <v>-42.34</v>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="C13" t="str">
         <v>603669</v>
       </c>
-      <c r="D13" s="145" t="str">
+      <c r="D13" s="156" t="str">
         <v>净卖: -338.04万</v>
       </c>
       <c r="E13">
@@ -4595,41 +4595,41 @@
       <c r="H13">
         <v>0.7</v>
       </c>
-      <c r="I13" s="146">
+      <c r="I13" s="152">
         <v>9.25</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="144">
         <v>9.77</v>
       </c>
-      <c r="K13" s="147">
+      <c r="K13" s="154">
         <v>10.65</v>
       </c>
-      <c r="L13" s="156">
+      <c r="L13" s="149">
         <v>8.9</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="145">
         <v>8.2</v>
       </c>
       <c r="N13" s="150">
         <v>7.33</v>
       </c>
-      <c r="O13" s="153">
+      <c r="O13" s="151">
         <v>4.36</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="146">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="147">
         <v>1.05</v>
       </c>
-      <c r="R13" s="144">
+      <c r="R13" s="155">
         <v>4.71</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="148">
         <v>3.84</v>
       </c>
-      <c r="T13" s="151">
-        <v>-21.99</v>
+      <c r="T13" s="153">
+        <v>-23.56</v>
       </c>
     </row>
     <row r="14">
@@ -4642,7 +4642,7 @@
       <c r="C14" t="str">
         <v>000029</v>
       </c>
-      <c r="D14" s="158" t="str">
+      <c r="D14" s="159" t="str">
         <v>净卖: -639.40万</v>
       </c>
       <c r="E14">
@@ -4657,41 +4657,41 @@
       <c r="H14">
         <v>-9.37</v>
       </c>
-      <c r="I14" s="163">
+      <c r="I14" s="160">
         <v>-0.7</v>
       </c>
-      <c r="J14" s="159">
+      <c r="J14" s="166">
         <v>-3</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="167">
         <v>-4.4</v>
       </c>
-      <c r="L14" s="165">
+      <c r="L14" s="161">
         <v>-2.57</v>
       </c>
-      <c r="M14" s="160">
+      <c r="M14" s="168">
         <v>-6.27</v>
       </c>
-      <c r="N14" s="161">
+      <c r="N14" s="169">
         <v>-6.34</v>
       </c>
-      <c r="O14" s="167">
+      <c r="O14" s="162">
         <v>-10.14</v>
       </c>
-      <c r="P14" s="168">
+      <c r="P14" s="157">
         <v>-5.84</v>
       </c>
-      <c r="Q14" s="169">
+      <c r="Q14" s="165">
         <v>-7.84</v>
       </c>
-      <c r="R14" s="162">
+      <c r="R14" s="158">
         <v>-9.34</v>
       </c>
-      <c r="S14" s="166">
+      <c r="S14" s="163">
         <v>-8.27</v>
       </c>
-      <c r="T14" s="157">
-        <v>-33.42</v>
+      <c r="T14" s="164">
+        <v>-33.52</v>
       </c>
     </row>
     <row r="15">
@@ -4704,7 +4704,7 @@
       <c r="C15" t="str">
         <v>002856</v>
       </c>
-      <c r="D15" s="176" t="str">
+      <c r="D15" s="181" t="str">
         <v>净买: 611.16万</v>
       </c>
       <c r="E15">
@@ -4719,41 +4719,41 @@
       <c r="H15">
         <v>-6.28</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="179">
         <v>17.36</v>
       </c>
-      <c r="J15" s="180">
+      <c r="J15" s="182">
         <v>12.95</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="173">
         <v>15.42</v>
       </c>
-      <c r="L15" s="179">
+      <c r="L15" s="174">
         <v>15.86</v>
       </c>
-      <c r="M15" s="171">
+      <c r="M15" s="176">
         <v>13.22</v>
       </c>
-      <c r="N15" s="172">
+      <c r="N15" s="170">
         <v>9.87</v>
       </c>
-      <c r="O15" s="173">
+      <c r="O15" s="177">
         <v>15.95</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="175">
         <v>16.56</v>
       </c>
-      <c r="Q15" s="174">
+      <c r="Q15" s="171">
         <v>14.8</v>
       </c>
-      <c r="R15" s="175">
+      <c r="R15" s="180">
         <v>11.45</v>
       </c>
-      <c r="S15" s="182">
+      <c r="S15" s="172">
         <v>5.55</v>
       </c>
-      <c r="T15" s="170">
-        <v>4.14</v>
+      <c r="T15" s="178">
+        <v>10.57</v>
       </c>
     </row>
     <row r="16">
@@ -4766,7 +4766,7 @@
       <c r="C16" t="str">
         <v>603017</v>
       </c>
-      <c r="D16" s="185" t="str">
+      <c r="D16" s="189" t="str">
         <v>净买: 1022.95万</v>
       </c>
       <c r="E16">
@@ -4781,41 +4781,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="194">
+      <c r="I16" s="193">
         <v>0</v>
       </c>
-      <c r="J16" s="190">
+      <c r="J16" s="183">
         <v>10</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="186">
         <v>-0.98</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="184">
         <v>-6.69</v>
       </c>
-      <c r="M16" s="187">
+      <c r="M16" s="190">
         <v>-9.32</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="194">
         <v>-9.55</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="195">
         <v>-8.87</v>
       </c>
       <c r="P16" s="191">
         <v>-9.25</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="185">
         <v>-7.74</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="187">
         <v>-3.68</v>
       </c>
-      <c r="S16" s="192">
+      <c r="S16" s="188">
         <v>-4.59</v>
       </c>
-      <c r="T16" s="193">
-        <v>6.84</v>
+      <c r="T16" s="192">
+        <v>17.52</v>
       </c>
     </row>
     <row r="17">
@@ -4877,40 +4877,40 @@
       <c r="F18" t="str"/>
       <c r="G18" t="str"/>
       <c r="H18" t="str"/>
-      <c r="I18" s="202">
+      <c r="I18" s="200">
         <v>40</v>
       </c>
-      <c r="J18" s="203">
+      <c r="J18" s="196">
         <v>60</v>
       </c>
-      <c r="K18" s="207">
+      <c r="K18" s="203">
         <v>53.33</v>
       </c>
-      <c r="L18" s="206">
+      <c r="L18" s="197">
         <v>46.67</v>
       </c>
-      <c r="M18" s="198">
+      <c r="M18" s="205">
         <v>53.33</v>
       </c>
-      <c r="N18" s="199">
+      <c r="N18" s="206">
         <v>53.33</v>
       </c>
-      <c r="O18" s="196">
+      <c r="O18" s="201">
         <v>53.33</v>
       </c>
-      <c r="P18" s="200">
+      <c r="P18" s="204">
         <v>60</v>
       </c>
-      <c r="Q18" s="204">
+      <c r="Q18" s="207">
         <v>53.33</v>
       </c>
-      <c r="R18" s="205">
+      <c r="R18" s="198">
         <v>53.33</v>
       </c>
-      <c r="S18" s="201">
+      <c r="S18" s="199">
         <v>53.33</v>
       </c>
-      <c r="T18" s="197">
+      <c r="T18" s="202">
         <v>53.33</v>
       </c>
     </row>
@@ -4925,41 +4925,41 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="209">
+      <c r="I19" s="213">
         <v>3.7</v>
       </c>
       <c r="J19" s="214">
         <v>3.35</v>
       </c>
-      <c r="K19" s="212">
+      <c r="K19" s="218">
         <v>2.78</v>
       </c>
-      <c r="L19" s="217">
+      <c r="L19" s="210">
         <v>3.08</v>
       </c>
-      <c r="M19" s="218">
+      <c r="M19" s="215">
         <v>5.09</v>
       </c>
-      <c r="N19" s="215">
+      <c r="N19" s="219">
         <v>4.08</v>
       </c>
-      <c r="O19" s="213">
+      <c r="O19" s="211">
         <v>5.66</v>
       </c>
-      <c r="P19" s="210">
+      <c r="P19" s="216">
         <v>9.79</v>
       </c>
-      <c r="Q19" s="219">
+      <c r="Q19" s="208">
         <v>11.41</v>
       </c>
-      <c r="R19" s="208">
+      <c r="R19" s="209">
         <v>13.65</v>
       </c>
-      <c r="S19" s="216">
+      <c r="S19" s="212">
         <v>17.55</v>
       </c>
-      <c r="T19" s="211">
-        <v>2.73</v>
+      <c r="T19" s="217">
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/落升(江南神鹰)/index.xlsx
+++ b/youzi/落升(江南神鹰)/index.xlsx
@@ -39,12 +39,72 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFBC2635"/>
         <bgColor/>
       </patternFill>
@@ -57,31 +117,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -93,7 +159,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF98D5A6"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -105,13 +171,1141 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA0D8AD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCF2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B5BB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,1231 +1317,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BCF9A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3898,7 +3898,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="5" t="str">
         <v>净买: 1815.37万</v>
       </c>
       <c r="E2">
@@ -3913,41 +3913,41 @@
       <c r="H2">
         <v>10.02</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="6">
         <v>0</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="10">
         <v>2.04</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="11">
         <v>4.88</v>
       </c>
-      <c r="L2" s="1">
+      <c r="L2" s="2">
         <v>7.07</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M2" s="12">
         <v>7.94</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="13">
         <v>10.06</v>
       </c>
-      <c r="O2" s="6">
+      <c r="O2" s="9">
         <v>21.06</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="1">
         <v>33.16</v>
       </c>
       <c r="Q2" s="3">
         <v>23.03</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="7">
         <v>25.8</v>
       </c>
-      <c r="S2" s="10">
+      <c r="S2" s="8">
         <v>24.05</v>
       </c>
-      <c r="T2" s="11">
-        <v>-34.18</v>
+      <c r="T2" s="4">
+        <v>-34.77</v>
       </c>
     </row>
     <row r="3">
@@ -3960,7 +3960,7 @@
       <c r="C3" t="str">
         <v>605588</v>
       </c>
-      <c r="D3" s="25" t="str">
+      <c r="D3" s="14" t="str">
         <v>净买: 1980.32万</v>
       </c>
       <c r="E3">
@@ -3975,41 +3975,41 @@
       <c r="H3">
         <v>10.01</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="20">
         <v>0</v>
       </c>
-      <c r="J3" s="14">
+      <c r="J3" s="15">
         <v>6.96</v>
       </c>
-      <c r="K3" s="15">
+      <c r="K3" s="25">
         <v>6.11</v>
       </c>
-      <c r="L3" s="23">
+      <c r="L3" s="21">
         <v>-2.38</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="22">
         <v>-10.29</v>
       </c>
-      <c r="N3" s="16">
+      <c r="N3" s="23">
         <v>-19.26</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="17">
         <v>-18.34</v>
       </c>
-      <c r="P3" s="17">
+      <c r="P3" s="18">
         <v>-18.05</v>
       </c>
-      <c r="Q3" s="21">
+      <c r="Q3" s="16">
         <v>-17.13</v>
       </c>
-      <c r="R3" s="24">
+      <c r="R3" s="26">
         <v>-13.31</v>
       </c>
-      <c r="S3" s="19">
+      <c r="S3" s="24">
         <v>-13.66</v>
       </c>
-      <c r="T3" s="22">
-        <v>4.97</v>
+      <c r="T3" s="19">
+        <v>6.52</v>
       </c>
     </row>
     <row r="4">
@@ -4022,7 +4022,7 @@
       <c r="C4" t="str">
         <v>002165</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="28" t="str">
         <v>净买: 3957.43万</v>
       </c>
       <c r="E4">
@@ -4037,41 +4037,41 @@
       <c r="H4">
         <v>-10.02</v>
       </c>
-      <c r="I4" s="39">
+      <c r="I4" s="33">
         <v>22.26</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="38">
         <v>16.61</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="35">
         <v>28.28</v>
       </c>
-      <c r="L4" s="33">
+      <c r="L4" s="29">
         <v>18.25</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="36">
         <v>30.11</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="37">
         <v>29.56</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="39">
         <v>32.48</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="30">
         <v>40.15</v>
       </c>
-      <c r="Q4" s="30">
+      <c r="Q4" s="31">
         <v>48.54</v>
       </c>
-      <c r="R4" s="37">
+      <c r="R4" s="27">
         <v>63.32</v>
       </c>
-      <c r="S4" s="38">
+      <c r="S4" s="34">
         <v>79.74</v>
       </c>
-      <c r="T4" s="31">
-        <v>74.82</v>
+      <c r="T4" s="32">
+        <v>65.88</v>
       </c>
     </row>
     <row r="5">
@@ -4084,7 +4084,7 @@
       <c r="C5" t="str">
         <v>002165</v>
       </c>
-      <c r="D5" s="51" t="str">
+      <c r="D5" s="49" t="str">
         <v>净卖: -4519.88万</v>
       </c>
       <c r="E5">
@@ -4099,41 +4099,41 @@
       <c r="H5">
         <v>-8.21</v>
       </c>
-      <c r="I5" s="52">
+      <c r="I5" s="50">
         <v>3.9</v>
       </c>
-      <c r="J5" s="45">
+      <c r="J5" s="52">
         <v>14.31</v>
       </c>
-      <c r="K5" s="46">
+      <c r="K5" s="40">
         <v>5.37</v>
       </c>
-      <c r="L5" s="40">
+      <c r="L5" s="41">
         <v>15.93</v>
       </c>
-      <c r="M5" s="41">
+      <c r="M5" s="43">
         <v>15.45</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="44">
         <v>18.05</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="46">
         <v>24.88</v>
       </c>
-      <c r="P5" s="47">
+      <c r="P5" s="51">
         <v>32.36</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="45">
         <v>45.53</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="42">
         <v>60.16</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="47">
         <v>76.26</v>
       </c>
-      <c r="T5" s="44">
-        <v>55.77</v>
+      <c r="T5" s="48">
+        <v>47.8</v>
       </c>
     </row>
     <row r="6">
@@ -4146,7 +4146,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="53" t="str">
         <v>净买: 1976.41万</v>
       </c>
       <c r="E6">
@@ -4161,41 +4161,41 @@
       <c r="H6">
         <v>10</v>
       </c>
-      <c r="I6" s="62">
+      <c r="I6" s="58">
         <v>0</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="54">
         <v>9.93</v>
       </c>
-      <c r="K6" s="57">
+      <c r="K6" s="55">
         <v>20.88</v>
       </c>
-      <c r="L6" s="63">
+      <c r="L6" s="62">
         <v>33</v>
       </c>
-      <c r="M6" s="58">
+      <c r="M6" s="63">
         <v>43.1</v>
       </c>
       <c r="N6" s="64">
         <v>28.79</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="59">
         <v>19.36</v>
       </c>
-      <c r="P6" s="53">
+      <c r="P6" s="65">
         <v>21.55</v>
       </c>
       <c r="Q6" s="60">
         <v>9.43</v>
       </c>
-      <c r="R6" s="54">
+      <c r="R6" s="61">
         <v>4.04</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="56">
         <v>4.38</v>
       </c>
-      <c r="T6" s="61">
-        <v>-2.69</v>
+      <c r="T6" s="57">
+        <v>-2.19</v>
       </c>
     </row>
     <row r="7">
@@ -4208,7 +4208,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -2117.52万</v>
       </c>
       <c r="E7">
@@ -4223,41 +4223,41 @@
       <c r="H7">
         <v>7.72</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="74">
         <v>2.15</v>
       </c>
-      <c r="J7" s="70">
+      <c r="J7" s="71">
         <v>1.72</v>
       </c>
-      <c r="K7" s="76">
+      <c r="K7" s="72">
         <v>4.01</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="73">
         <v>10.03</v>
       </c>
-      <c r="M7" s="77">
+      <c r="M7" s="78">
         <v>16.62</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="75">
         <v>28.22</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="66">
         <v>41.12</v>
       </c>
-      <c r="P7" s="71">
+      <c r="P7" s="67">
         <v>55.3</v>
       </c>
-      <c r="Q7" s="75">
+      <c r="Q7" s="68">
         <v>70.77</v>
       </c>
-      <c r="R7" s="72">
+      <c r="R7" s="69">
         <v>73.21</v>
       </c>
-      <c r="S7" s="69">
+      <c r="S7" s="76">
         <v>90.54</v>
       </c>
-      <c r="T7" s="73">
-        <v>37.25</v>
+      <c r="T7" s="77">
+        <v>30.23</v>
       </c>
     </row>
     <row r="8">
@@ -4285,41 +4285,41 @@
       <c r="H8">
         <v>-5.06</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="81">
         <v>-5.2</v>
       </c>
-      <c r="J8" s="79">
+      <c r="J8" s="90">
         <v>-2.53</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="91">
         <v>-6.53</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="82">
         <v>-6.07</v>
       </c>
-      <c r="M8" s="81">
+      <c r="M8" s="85">
         <v>-4.07</v>
       </c>
-      <c r="N8" s="89">
+      <c r="N8" s="83">
         <v>-13.67</v>
       </c>
-      <c r="O8" s="82">
+      <c r="O8" s="86">
         <v>-17</v>
       </c>
-      <c r="P8" s="86">
+      <c r="P8" s="84">
         <v>-19.33</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="79">
         <v>-16</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="89">
         <v>-17.47</v>
       </c>
-      <c r="S8" s="84">
+      <c r="S8" s="87">
         <v>-15</v>
       </c>
-      <c r="T8" s="91">
-        <v>-18</v>
+      <c r="T8" s="80">
+        <v>-18.73</v>
       </c>
     </row>
     <row r="9">
@@ -4332,7 +4332,7 @@
       <c r="C9" t="str">
         <v>000965</v>
       </c>
-      <c r="D9" s="93" t="str">
+      <c r="D9" s="99" t="str">
         <v>净卖: -66.63万</v>
       </c>
       <c r="E9">
@@ -4347,41 +4347,41 @@
       <c r="H9">
         <v>0.31</v>
       </c>
-      <c r="I9" s="100">
+      <c r="I9" s="92">
         <v>8.75</v>
       </c>
-      <c r="J9" s="98">
+      <c r="J9" s="93">
         <v>-1.56</v>
       </c>
-      <c r="K9" s="103">
+      <c r="K9" s="95">
         <v>-0.94</v>
       </c>
-      <c r="L9" s="94">
+      <c r="L9" s="96">
         <v>-3.75</v>
       </c>
-      <c r="M9" s="95">
+      <c r="M9" s="98">
         <v>5.94</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="100">
         <v>16.56</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="101">
         <v>28.12</v>
       </c>
-      <c r="P9" s="101">
+      <c r="P9" s="102">
         <v>40.94</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="94">
         <v>55</v>
       </c>
-      <c r="R9" s="97">
+      <c r="R9" s="103">
         <v>48.12</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="97">
         <v>62.81</v>
       </c>
-      <c r="T9" s="92">
-        <v>12.81</v>
+      <c r="T9" s="104">
+        <v>10.62</v>
       </c>
     </row>
     <row r="10">
@@ -4394,7 +4394,7 @@
       <c r="C10" t="str">
         <v>002981</v>
       </c>
-      <c r="D10" s="110" t="str">
+      <c r="D10" s="105" t="str">
         <v>净买: 1574.45万</v>
       </c>
       <c r="E10">
@@ -4409,41 +4409,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="111">
+      <c r="I10" s="112">
         <v>-0.74</v>
       </c>
-      <c r="J10" s="106">
+      <c r="J10" s="113">
         <v>-10.6</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="106">
         <v>-14.1</v>
       </c>
       <c r="L10" s="107">
         <v>-12.78</v>
       </c>
-      <c r="M10" s="108">
+      <c r="M10" s="114">
         <v>-4.07</v>
       </c>
-      <c r="N10" s="115">
+      <c r="N10" s="108">
         <v>-3.06</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="109">
         <v>-6.09</v>
       </c>
-      <c r="P10" s="116">
+      <c r="P10" s="110">
         <v>3.33</v>
       </c>
-      <c r="Q10" s="114">
+      <c r="Q10" s="111">
         <v>-2.01</v>
       </c>
-      <c r="R10" s="109">
+      <c r="R10" s="115">
         <v>-1.88</v>
       </c>
-      <c r="S10" s="117">
+      <c r="S10" s="116">
         <v>-4.77</v>
       </c>
-      <c r="T10" s="105">
-        <v>6.96</v>
+      <c r="T10" s="117">
+        <v>6.22</v>
       </c>
     </row>
     <row r="11">
@@ -4456,7 +4456,7 @@
       <c r="C11" t="str">
         <v>600794</v>
       </c>
-      <c r="D11" s="122" t="str">
+      <c r="D11" s="124" t="str">
         <v>净卖: -697.77万</v>
       </c>
       <c r="E11">
@@ -4471,41 +4471,41 @@
       <c r="H11">
         <v>-8.75</v>
       </c>
-      <c r="I11" s="123">
+      <c r="I11" s="120">
         <v>-1.46</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="118">
         <v>-11.25</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="128">
         <v>-17.08</v>
       </c>
-      <c r="L11" s="120">
+      <c r="L11" s="119">
         <v>-14.37</v>
       </c>
       <c r="M11" s="125">
         <v>-11.67</v>
       </c>
-      <c r="N11" s="129">
+      <c r="N11" s="121">
         <v>-12.71</v>
       </c>
-      <c r="O11" s="130">
+      <c r="O11" s="126">
         <v>-15.42</v>
       </c>
-      <c r="P11" s="126">
+      <c r="P11" s="129">
         <v>-15.42</v>
       </c>
-      <c r="Q11" s="118">
+      <c r="Q11" s="122">
         <v>-12.29</v>
       </c>
-      <c r="R11" s="119">
+      <c r="R11" s="123">
         <v>-3.54</v>
       </c>
-      <c r="S11" s="121">
+      <c r="S11" s="127">
         <v>-0.83</v>
       </c>
-      <c r="T11" s="128">
-        <v>-25.62</v>
+      <c r="T11" s="130">
+        <v>-24.79</v>
       </c>
     </row>
     <row r="12">
@@ -4518,7 +4518,7 @@
       <c r="C12" t="str">
         <v>000627</v>
       </c>
-      <c r="D12" s="135" t="str">
+      <c r="D12" s="133" t="str">
         <v>净买: 1535.97万</v>
       </c>
       <c r="E12">
@@ -4533,40 +4533,40 @@
       <c r="H12">
         <v>-9.87</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="142">
         <v>0</v>
       </c>
-      <c r="J12" s="133">
+      <c r="J12" s="134">
         <v>-5.11</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="135">
         <v>-9.85</v>
       </c>
-      <c r="L12" s="142">
+      <c r="L12" s="138">
         <v>-14.23</v>
       </c>
-      <c r="M12" s="143">
+      <c r="M12" s="139">
         <v>-18.61</v>
       </c>
-      <c r="N12" s="137">
+      <c r="N12" s="143">
         <v>-22.63</v>
       </c>
       <c r="O12" s="131">
         <v>-26.64</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="136">
         <v>-30.29</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="137">
         <v>-33.94</v>
       </c>
-      <c r="R12" s="139">
+      <c r="R12" s="141">
         <v>-36.86</v>
       </c>
-      <c r="S12" s="141">
+      <c r="S12" s="140">
         <v>-36.86</v>
       </c>
-      <c r="T12" s="134">
+      <c r="T12" s="132">
         <v>-42.34</v>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="C13" t="str">
         <v>603669</v>
       </c>
-      <c r="D13" s="156" t="str">
+      <c r="D13" s="147" t="str">
         <v>净卖: -338.04万</v>
       </c>
       <c r="E13">
@@ -4595,41 +4595,41 @@
       <c r="H13">
         <v>0.7</v>
       </c>
-      <c r="I13" s="152">
+      <c r="I13" s="148">
         <v>9.25</v>
       </c>
-      <c r="J13" s="144">
+      <c r="J13" s="150">
         <v>9.77</v>
       </c>
-      <c r="K13" s="154">
+      <c r="K13" s="153">
         <v>10.65</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="151">
         <v>8.9</v>
       </c>
-      <c r="M13" s="145">
+      <c r="M13" s="152">
         <v>8.2</v>
       </c>
-      <c r="N13" s="150">
+      <c r="N13" s="144">
         <v>7.33</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="145">
         <v>4.36</v>
       </c>
-      <c r="P13" s="146">
+      <c r="P13" s="154">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="Q13" s="149">
         <v>1.05</v>
       </c>
       <c r="R13" s="155">
         <v>4.71</v>
       </c>
-      <c r="S13" s="148">
+      <c r="S13" s="156">
         <v>3.84</v>
       </c>
-      <c r="T13" s="153">
-        <v>-23.56</v>
+      <c r="T13" s="146">
+        <v>-25.48</v>
       </c>
     </row>
     <row r="14">
@@ -4642,7 +4642,7 @@
       <c r="C14" t="str">
         <v>000029</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="161" t="str">
         <v>净卖: -639.40万</v>
       </c>
       <c r="E14">
@@ -4657,41 +4657,41 @@
       <c r="H14">
         <v>-9.37</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="165">
         <v>-0.7</v>
       </c>
       <c r="J14" s="166">
         <v>-3</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="162">
         <v>-4.4</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="168">
         <v>-2.57</v>
       </c>
-      <c r="M14" s="168">
+      <c r="M14" s="157">
         <v>-6.27</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="167">
         <v>-6.34</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="158">
         <v>-10.14</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="163">
         <v>-5.84</v>
       </c>
-      <c r="Q14" s="165">
+      <c r="Q14" s="164">
         <v>-7.84</v>
       </c>
-      <c r="R14" s="158">
+      <c r="R14" s="169">
         <v>-9.34</v>
       </c>
-      <c r="S14" s="163">
+      <c r="S14" s="159">
         <v>-8.27</v>
       </c>
-      <c r="T14" s="164">
-        <v>-33.52</v>
+      <c r="T14" s="160">
+        <v>-32.72</v>
       </c>
     </row>
     <row r="15">
@@ -4704,7 +4704,7 @@
       <c r="C15" t="str">
         <v>002856</v>
       </c>
-      <c r="D15" s="181" t="str">
+      <c r="D15" s="182" t="str">
         <v>净买: 611.16万</v>
       </c>
       <c r="E15">
@@ -4719,41 +4719,41 @@
       <c r="H15">
         <v>-6.28</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="170">
         <v>17.36</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="177">
         <v>12.95</v>
       </c>
-      <c r="K15" s="173">
+      <c r="K15" s="171">
         <v>15.42</v>
       </c>
       <c r="L15" s="174">
         <v>15.86</v>
       </c>
-      <c r="M15" s="176">
+      <c r="M15" s="175">
         <v>13.22</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="180">
         <v>9.87</v>
       </c>
-      <c r="O15" s="177">
+      <c r="O15" s="172">
         <v>15.95</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="176">
         <v>16.56</v>
       </c>
-      <c r="Q15" s="171">
+      <c r="Q15" s="173">
         <v>14.8</v>
       </c>
-      <c r="R15" s="180">
+      <c r="R15" s="181">
         <v>11.45</v>
       </c>
-      <c r="S15" s="172">
+      <c r="S15" s="178">
         <v>5.55</v>
       </c>
-      <c r="T15" s="178">
-        <v>10.57</v>
+      <c r="T15" s="179">
+        <v>9.96</v>
       </c>
     </row>
     <row r="16">
@@ -4766,7 +4766,7 @@
       <c r="C16" t="str">
         <v>603017</v>
       </c>
-      <c r="D16" s="189" t="str">
+      <c r="D16" s="190" t="str">
         <v>净买: 1022.95万</v>
       </c>
       <c r="E16">
@@ -4781,41 +4781,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="184">
         <v>0</v>
       </c>
-      <c r="J16" s="183">
+      <c r="J16" s="185">
         <v>10</v>
       </c>
       <c r="K16" s="186">
         <v>-0.98</v>
       </c>
-      <c r="L16" s="184">
+      <c r="L16" s="191">
         <v>-6.69</v>
       </c>
-      <c r="M16" s="190">
+      <c r="M16" s="194">
         <v>-9.32</v>
       </c>
-      <c r="N16" s="194">
+      <c r="N16" s="195">
         <v>-9.55</v>
       </c>
-      <c r="O16" s="195">
+      <c r="O16" s="187">
         <v>-8.87</v>
       </c>
-      <c r="P16" s="191">
+      <c r="P16" s="188">
         <v>-9.25</v>
       </c>
-      <c r="Q16" s="185">
+      <c r="Q16" s="192">
         <v>-7.74</v>
       </c>
-      <c r="R16" s="187">
+      <c r="R16" s="193">
         <v>-3.68</v>
       </c>
-      <c r="S16" s="188">
+      <c r="S16" s="189">
         <v>-4.59</v>
       </c>
-      <c r="T16" s="192">
-        <v>17.52</v>
+      <c r="T16" s="183">
+        <v>14.74</v>
       </c>
     </row>
     <row r="17">
@@ -4877,40 +4877,40 @@
       <c r="F18" t="str"/>
       <c r="G18" t="str"/>
       <c r="H18" t="str"/>
-      <c r="I18" s="200">
+      <c r="I18" s="204">
         <v>40</v>
       </c>
-      <c r="J18" s="196">
+      <c r="J18" s="200">
         <v>60</v>
       </c>
-      <c r="K18" s="203">
+      <c r="K18" s="198">
         <v>53.33</v>
       </c>
-      <c r="L18" s="197">
+      <c r="L18" s="201">
         <v>46.67</v>
       </c>
-      <c r="M18" s="205">
+      <c r="M18" s="206">
         <v>53.33</v>
       </c>
-      <c r="N18" s="206">
+      <c r="N18" s="199">
         <v>53.33</v>
       </c>
-      <c r="O18" s="201">
+      <c r="O18" s="202">
         <v>53.33</v>
       </c>
-      <c r="P18" s="204">
+      <c r="P18" s="207">
         <v>60</v>
       </c>
-      <c r="Q18" s="207">
+      <c r="Q18" s="205">
         <v>53.33</v>
       </c>
-      <c r="R18" s="198">
+      <c r="R18" s="196">
         <v>53.33</v>
       </c>
-      <c r="S18" s="199">
+      <c r="S18" s="197">
         <v>53.33</v>
       </c>
-      <c r="T18" s="202">
+      <c r="T18" s="203">
         <v>53.33</v>
       </c>
     </row>
@@ -4925,41 +4925,41 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="213">
+      <c r="I19" s="211">
         <v>3.7</v>
       </c>
-      <c r="J19" s="214">
+      <c r="J19" s="219">
         <v>3.35</v>
       </c>
-      <c r="K19" s="218">
+      <c r="K19" s="213">
         <v>2.78</v>
       </c>
-      <c r="L19" s="210">
+      <c r="L19" s="208">
         <v>3.08</v>
       </c>
       <c r="M19" s="215">
         <v>5.09</v>
       </c>
-      <c r="N19" s="219">
+      <c r="N19" s="214">
         <v>4.08</v>
       </c>
-      <c r="O19" s="211">
+      <c r="O19" s="216">
         <v>5.66</v>
       </c>
-      <c r="P19" s="216">
+      <c r="P19" s="209">
         <v>9.79</v>
       </c>
-      <c r="Q19" s="208">
+      <c r="Q19" s="217">
         <v>11.41</v>
       </c>
-      <c r="R19" s="209">
+      <c r="R19" s="218">
         <v>13.65</v>
       </c>
       <c r="S19" s="212">
         <v>17.55</v>
       </c>
-      <c r="T19" s="217">
-        <v>2.72</v>
+      <c r="T19" s="210">
+        <v>0.73</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/落升(江南神鹰)/index.xlsx
+++ b/youzi/落升(江南神鹰)/index.xlsx
@@ -39,7 +39,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0ACB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2635"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3949"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -57,6 +81,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -69,43 +105,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0ACB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3949"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2635"/>
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,805 +219,1111 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBC2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC72B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA0D8AD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCF2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -933,349 +1335,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
+        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -1288,66 +1348,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B5BB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3898,7 +3898,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="5" t="str">
+      <c r="D2" s="11" t="str">
         <v>净买: 1815.37万</v>
       </c>
       <c r="E2">
@@ -3913,41 +3913,41 @@
       <c r="H2">
         <v>10.02</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="J2" s="10">
+      <c r="J2" s="2">
         <v>2.04</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="5">
         <v>4.88</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="6">
         <v>7.07</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="3">
         <v>7.94</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="12">
         <v>10.06</v>
       </c>
-      <c r="O2" s="9">
+      <c r="O2" s="13">
         <v>21.06</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="7">
         <v>33.16</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="8">
         <v>23.03</v>
       </c>
-      <c r="R2" s="7">
+      <c r="R2" s="4">
         <v>25.8</v>
       </c>
-      <c r="S2" s="8">
+      <c r="S2" s="9">
         <v>24.05</v>
       </c>
-      <c r="T2" s="4">
-        <v>-34.77</v>
+      <c r="T2" s="10">
+        <v>-33.89</v>
       </c>
     </row>
     <row r="3">
@@ -3960,7 +3960,7 @@
       <c r="C3" t="str">
         <v>605588</v>
       </c>
-      <c r="D3" s="14" t="str">
+      <c r="D3" s="17" t="str">
         <v>净买: 1980.32万</v>
       </c>
       <c r="E3">
@@ -3975,41 +3975,41 @@
       <c r="H3">
         <v>10.01</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="23">
         <v>0</v>
       </c>
-      <c r="J3" s="15">
+      <c r="J3" s="18">
         <v>6.96</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="24">
         <v>6.11</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="15">
         <v>-2.38</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="16">
         <v>-10.29</v>
       </c>
-      <c r="N3" s="23">
+      <c r="N3" s="19">
         <v>-19.26</v>
       </c>
-      <c r="O3" s="17">
+      <c r="O3" s="21">
         <v>-18.34</v>
       </c>
-      <c r="P3" s="18">
+      <c r="P3" s="22">
         <v>-18.05</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="Q3" s="20">
         <v>-17.13</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="25">
         <v>-13.31</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="26">
         <v>-13.66</v>
       </c>
-      <c r="T3" s="19">
-        <v>6.52</v>
+      <c r="T3" s="14">
+        <v>6.13</v>
       </c>
     </row>
     <row r="4">
@@ -4022,7 +4022,7 @@
       <c r="C4" t="str">
         <v>002165</v>
       </c>
-      <c r="D4" s="28" t="str">
+      <c r="D4" s="30" t="str">
         <v>净买: 3957.43万</v>
       </c>
       <c r="E4">
@@ -4037,41 +4037,41 @@
       <c r="H4">
         <v>-10.02</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="31">
         <v>22.26</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="37">
         <v>16.61</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="32">
         <v>28.28</v>
       </c>
-      <c r="L4" s="29">
+      <c r="L4" s="38">
         <v>18.25</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="39">
         <v>30.11</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="34">
         <v>29.56</v>
       </c>
-      <c r="O4" s="39">
+      <c r="O4" s="27">
         <v>32.48</v>
       </c>
-      <c r="P4" s="30">
+      <c r="P4" s="35">
         <v>40.15</v>
       </c>
-      <c r="Q4" s="31">
+      <c r="Q4" s="33">
         <v>48.54</v>
       </c>
-      <c r="R4" s="27">
+      <c r="R4" s="36">
         <v>63.32</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="28">
         <v>79.74</v>
       </c>
-      <c r="T4" s="32">
-        <v>65.88</v>
+      <c r="T4" s="29">
+        <v>60.04</v>
       </c>
     </row>
     <row r="5">
@@ -4084,7 +4084,7 @@
       <c r="C5" t="str">
         <v>002165</v>
       </c>
-      <c r="D5" s="49" t="str">
+      <c r="D5" s="46" t="str">
         <v>净卖: -4519.88万</v>
       </c>
       <c r="E5">
@@ -4099,41 +4099,41 @@
       <c r="H5">
         <v>-8.21</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="42">
         <v>3.9</v>
       </c>
-      <c r="J5" s="52">
+      <c r="J5" s="47">
         <v>14.31</v>
       </c>
-      <c r="K5" s="40">
+      <c r="K5" s="43">
         <v>5.37</v>
       </c>
-      <c r="L5" s="41">
+      <c r="L5" s="44">
         <v>15.93</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="45">
         <v>15.45</v>
       </c>
-      <c r="N5" s="44">
+      <c r="N5" s="52">
         <v>18.05</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="48">
         <v>24.88</v>
       </c>
-      <c r="P5" s="51">
+      <c r="P5" s="40">
         <v>32.36</v>
       </c>
-      <c r="Q5" s="45">
+      <c r="Q5" s="41">
         <v>45.53</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="49">
         <v>60.16</v>
       </c>
-      <c r="S5" s="47">
+      <c r="S5" s="50">
         <v>76.26</v>
       </c>
-      <c r="T5" s="48">
-        <v>47.8</v>
+      <c r="T5" s="51">
+        <v>42.6</v>
       </c>
     </row>
     <row r="6">
@@ -4146,7 +4146,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="53" t="str">
+      <c r="D6" s="62" t="str">
         <v>净买: 1976.41万</v>
       </c>
       <c r="E6">
@@ -4161,41 +4161,41 @@
       <c r="H6">
         <v>10</v>
       </c>
-      <c r="I6" s="58">
+      <c r="I6" s="65">
         <v>0</v>
       </c>
-      <c r="J6" s="54">
+      <c r="J6" s="61">
         <v>9.93</v>
       </c>
-      <c r="K6" s="55">
+      <c r="K6" s="53">
         <v>20.88</v>
       </c>
-      <c r="L6" s="62">
+      <c r="L6" s="58">
         <v>33</v>
       </c>
-      <c r="M6" s="63">
+      <c r="M6" s="54">
         <v>43.1</v>
       </c>
-      <c r="N6" s="64">
+      <c r="N6" s="55">
         <v>28.79</v>
       </c>
-      <c r="O6" s="59">
+      <c r="O6" s="63">
         <v>19.36</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="59">
         <v>21.55</v>
       </c>
       <c r="Q6" s="60">
         <v>9.43</v>
       </c>
-      <c r="R6" s="61">
+      <c r="R6" s="56">
         <v>4.04</v>
       </c>
-      <c r="S6" s="56">
+      <c r="S6" s="64">
         <v>4.38</v>
       </c>
       <c r="T6" s="57">
-        <v>-2.19</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="7">
@@ -4208,7 +4208,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="70" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -2117.52万</v>
       </c>
       <c r="E7">
@@ -4223,41 +4223,41 @@
       <c r="H7">
         <v>7.72</v>
       </c>
-      <c r="I7" s="74">
+      <c r="I7" s="75">
         <v>2.15</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="67">
         <v>1.72</v>
       </c>
       <c r="K7" s="72">
         <v>4.01</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="70">
         <v>10.03</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="73">
         <v>16.62</v>
       </c>
-      <c r="N7" s="75">
+      <c r="N7" s="76">
         <v>28.22</v>
       </c>
-      <c r="O7" s="66">
+      <c r="O7" s="68">
         <v>41.12</v>
       </c>
-      <c r="P7" s="67">
+      <c r="P7" s="77">
         <v>55.3</v>
       </c>
-      <c r="Q7" s="68">
+      <c r="Q7" s="78">
         <v>70.77</v>
       </c>
       <c r="R7" s="69">
         <v>73.21</v>
       </c>
-      <c r="S7" s="76">
+      <c r="S7" s="71">
         <v>90.54</v>
       </c>
-      <c r="T7" s="77">
-        <v>30.23</v>
+      <c r="T7" s="66">
+        <v>25.64</v>
       </c>
     </row>
     <row r="8">
@@ -4270,7 +4270,7 @@
       <c r="C8" t="str">
         <v>002923</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="89" t="str">
         <v>净买: 1689.05万</v>
       </c>
       <c r="E8">
@@ -4288,38 +4288,38 @@
       <c r="I8" s="81">
         <v>-5.2</v>
       </c>
-      <c r="J8" s="90">
+      <c r="J8" s="84">
         <v>-2.53</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="85">
         <v>-6.53</v>
       </c>
       <c r="L8" s="82">
         <v>-6.07</v>
       </c>
-      <c r="M8" s="85">
+      <c r="M8" s="86">
         <v>-4.07</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="90">
         <v>-13.67</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="87">
         <v>-17</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="88">
         <v>-19.33</v>
       </c>
       <c r="Q8" s="79">
         <v>-16</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="83">
         <v>-17.47</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="80">
         <v>-15</v>
       </c>
-      <c r="T8" s="80">
-        <v>-18.73</v>
+      <c r="T8" s="91">
+        <v>-16.4</v>
       </c>
     </row>
     <row r="9">
@@ -4332,7 +4332,7 @@
       <c r="C9" t="str">
         <v>000965</v>
       </c>
-      <c r="D9" s="99" t="str">
+      <c r="D9" s="104" t="str">
         <v>净卖: -66.63万</v>
       </c>
       <c r="E9">
@@ -4347,41 +4347,41 @@
       <c r="H9">
         <v>0.31</v>
       </c>
-      <c r="I9" s="92">
+      <c r="I9" s="96">
         <v>8.75</v>
       </c>
-      <c r="J9" s="93">
+      <c r="J9" s="92">
         <v>-1.56</v>
       </c>
-      <c r="K9" s="95">
+      <c r="K9" s="98">
         <v>-0.94</v>
       </c>
-      <c r="L9" s="96">
+      <c r="L9" s="93">
         <v>-3.75</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="99">
         <v>5.94</v>
       </c>
-      <c r="N9" s="100">
+      <c r="N9" s="94">
         <v>16.56</v>
       </c>
-      <c r="O9" s="101">
+      <c r="O9" s="102">
         <v>28.12</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="97">
         <v>40.94</v>
       </c>
-      <c r="Q9" s="94">
+      <c r="Q9" s="100">
         <v>55</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="95">
         <v>48.12</v>
       </c>
-      <c r="S9" s="97">
+      <c r="S9" s="103">
         <v>62.81</v>
       </c>
-      <c r="T9" s="104">
-        <v>10.62</v>
+      <c r="T9" s="101">
+        <v>11.87</v>
       </c>
     </row>
     <row r="10">
@@ -4394,7 +4394,7 @@
       <c r="C10" t="str">
         <v>002981</v>
       </c>
-      <c r="D10" s="105" t="str">
+      <c r="D10" s="110" t="str">
         <v>净买: 1574.45万</v>
       </c>
       <c r="E10">
@@ -4409,41 +4409,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="112">
+      <c r="I10" s="106">
         <v>-0.74</v>
       </c>
-      <c r="J10" s="113">
+      <c r="J10" s="111">
         <v>-10.6</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="112">
         <v>-14.1</v>
       </c>
-      <c r="L10" s="107">
+      <c r="L10" s="108">
         <v>-12.78</v>
       </c>
-      <c r="M10" s="114">
+      <c r="M10" s="113">
         <v>-4.07</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="109">
         <v>-3.06</v>
       </c>
-      <c r="O10" s="109">
+      <c r="O10" s="116">
         <v>-6.09</v>
       </c>
-      <c r="P10" s="110">
+      <c r="P10" s="114">
         <v>3.33</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="115">
         <v>-2.01</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="107">
         <v>-1.88</v>
       </c>
-      <c r="S10" s="116">
+      <c r="S10" s="117">
         <v>-4.77</v>
       </c>
-      <c r="T10" s="117">
-        <v>6.22</v>
+      <c r="T10" s="105">
+        <v>8.01</v>
       </c>
     </row>
     <row r="11">
@@ -4471,41 +4471,41 @@
       <c r="H11">
         <v>-8.75</v>
       </c>
-      <c r="I11" s="120">
+      <c r="I11" s="118">
         <v>-1.46</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="125">
         <v>-11.25</v>
       </c>
-      <c r="K11" s="128">
+      <c r="K11" s="126">
         <v>-17.08</v>
       </c>
       <c r="L11" s="119">
         <v>-14.37</v>
       </c>
-      <c r="M11" s="125">
+      <c r="M11" s="120">
         <v>-11.67</v>
       </c>
       <c r="N11" s="121">
         <v>-12.71</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="122">
         <v>-15.42</v>
       </c>
-      <c r="P11" s="129">
+      <c r="P11" s="127">
         <v>-15.42</v>
       </c>
-      <c r="Q11" s="122">
+      <c r="Q11" s="123">
         <v>-12.29</v>
       </c>
-      <c r="R11" s="123">
+      <c r="R11" s="128">
         <v>-3.54</v>
       </c>
-      <c r="S11" s="127">
+      <c r="S11" s="129">
         <v>-0.83</v>
       </c>
       <c r="T11" s="130">
-        <v>-24.79</v>
+        <v>-25</v>
       </c>
     </row>
     <row r="12">
@@ -4518,7 +4518,7 @@
       <c r="C12" t="str">
         <v>000627</v>
       </c>
-      <c r="D12" s="133" t="str">
+      <c r="D12" s="142" t="str">
         <v>净买: 1535.97万</v>
       </c>
       <c r="E12">
@@ -4533,40 +4533,40 @@
       <c r="H12">
         <v>-9.87</v>
       </c>
-      <c r="I12" s="142">
+      <c r="I12" s="143">
         <v>0</v>
       </c>
       <c r="J12" s="134">
         <v>-5.11</v>
       </c>
-      <c r="K12" s="135">
+      <c r="K12" s="139">
         <v>-9.85</v>
       </c>
-      <c r="L12" s="138">
+      <c r="L12" s="135">
         <v>-14.23</v>
       </c>
-      <c r="M12" s="139">
+      <c r="M12" s="131">
         <v>-18.61</v>
       </c>
-      <c r="N12" s="143">
+      <c r="N12" s="136">
         <v>-22.63</v>
       </c>
-      <c r="O12" s="131">
+      <c r="O12" s="132">
         <v>-26.64</v>
       </c>
-      <c r="P12" s="136">
+      <c r="P12" s="133">
         <v>-30.29</v>
       </c>
       <c r="Q12" s="137">
         <v>-33.94</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="138">
         <v>-36.86</v>
       </c>
       <c r="S12" s="140">
         <v>-36.86</v>
       </c>
-      <c r="T12" s="132">
+      <c r="T12" s="141">
         <v>-42.34</v>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="C13" t="str">
         <v>603669</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="144" t="str">
         <v>净卖: -338.04万</v>
       </c>
       <c r="E13">
@@ -4595,40 +4595,40 @@
       <c r="H13">
         <v>0.7</v>
       </c>
-      <c r="I13" s="148">
+      <c r="I13" s="145">
         <v>9.25</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="152">
         <v>9.77</v>
       </c>
-      <c r="K13" s="153">
+      <c r="K13" s="150">
         <v>10.65</v>
       </c>
-      <c r="L13" s="151">
+      <c r="L13" s="146">
         <v>8.9</v>
       </c>
-      <c r="M13" s="152">
+      <c r="M13" s="147">
         <v>8.2</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="153">
         <v>7.33</v>
       </c>
-      <c r="O13" s="145">
+      <c r="O13" s="155">
         <v>4.36</v>
       </c>
-      <c r="P13" s="154">
+      <c r="P13" s="156">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="149">
+      <c r="Q13" s="154">
         <v>1.05</v>
       </c>
-      <c r="R13" s="155">
+      <c r="R13" s="148">
         <v>4.71</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="149">
         <v>3.84</v>
       </c>
-      <c r="T13" s="146">
+      <c r="T13" s="151">
         <v>-25.48</v>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       <c r="C14" t="str">
         <v>000029</v>
       </c>
-      <c r="D14" s="161" t="str">
+      <c r="D14" s="159" t="str">
         <v>净卖: -639.40万</v>
       </c>
       <c r="E14">
@@ -4657,41 +4657,41 @@
       <c r="H14">
         <v>-9.37</v>
       </c>
-      <c r="I14" s="165">
+      <c r="I14" s="162">
         <v>-0.7</v>
       </c>
-      <c r="J14" s="166">
+      <c r="J14" s="163">
         <v>-3</v>
       </c>
-      <c r="K14" s="162">
+      <c r="K14" s="166">
         <v>-4.4</v>
       </c>
-      <c r="L14" s="168">
+      <c r="L14" s="160">
         <v>-2.57</v>
       </c>
       <c r="M14" s="157">
         <v>-6.27</v>
       </c>
-      <c r="N14" s="167">
+      <c r="N14" s="164">
         <v>-6.34</v>
       </c>
-      <c r="O14" s="158">
+      <c r="O14" s="165">
         <v>-10.14</v>
       </c>
-      <c r="P14" s="163">
+      <c r="P14" s="167">
         <v>-5.84</v>
       </c>
-      <c r="Q14" s="164">
+      <c r="Q14" s="168">
         <v>-7.84</v>
       </c>
       <c r="R14" s="169">
         <v>-9.34</v>
       </c>
-      <c r="S14" s="159">
+      <c r="S14" s="161">
         <v>-8.27</v>
       </c>
-      <c r="T14" s="160">
-        <v>-32.72</v>
+      <c r="T14" s="158">
+        <v>-30.82</v>
       </c>
     </row>
     <row r="15">
@@ -4704,7 +4704,7 @@
       <c r="C15" t="str">
         <v>002856</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="176" t="str">
         <v>净买: 611.16万</v>
       </c>
       <c r="E15">
@@ -4719,41 +4719,41 @@
       <c r="H15">
         <v>-6.28</v>
       </c>
-      <c r="I15" s="170">
+      <c r="I15" s="171">
         <v>17.36</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="180">
         <v>12.95</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="182">
         <v>15.42</v>
       </c>
-      <c r="L15" s="174">
+      <c r="L15" s="177">
         <v>15.86</v>
       </c>
-      <c r="M15" s="175">
+      <c r="M15" s="178">
         <v>13.22</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="179">
         <v>9.87</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="170">
         <v>15.95</v>
       </c>
-      <c r="P15" s="176">
+      <c r="P15" s="181">
         <v>16.56</v>
       </c>
-      <c r="Q15" s="173">
+      <c r="Q15" s="172">
         <v>14.8</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="173">
         <v>11.45</v>
       </c>
-      <c r="S15" s="178">
+      <c r="S15" s="174">
         <v>5.55</v>
       </c>
-      <c r="T15" s="179">
-        <v>9.96</v>
+      <c r="T15" s="175">
+        <v>15.59</v>
       </c>
     </row>
     <row r="16">
@@ -4766,7 +4766,7 @@
       <c r="C16" t="str">
         <v>603017</v>
       </c>
-      <c r="D16" s="190" t="str">
+      <c r="D16" s="191" t="str">
         <v>净买: 1022.95万</v>
       </c>
       <c r="E16">
@@ -4781,41 +4781,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="184">
+      <c r="I16" s="192">
         <v>0</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="184">
         <v>10</v>
       </c>
-      <c r="K16" s="186">
+      <c r="K16" s="193">
         <v>-0.98</v>
       </c>
-      <c r="L16" s="191">
+      <c r="L16" s="185">
         <v>-6.69</v>
       </c>
-      <c r="M16" s="194">
+      <c r="M16" s="183">
         <v>-9.32</v>
       </c>
-      <c r="N16" s="195">
+      <c r="N16" s="188">
         <v>-9.55</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="194">
         <v>-8.87</v>
       </c>
-      <c r="P16" s="188">
+      <c r="P16" s="186">
         <v>-9.25</v>
       </c>
-      <c r="Q16" s="192">
+      <c r="Q16" s="189">
         <v>-7.74</v>
       </c>
-      <c r="R16" s="193">
+      <c r="R16" s="195">
         <v>-3.68</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="190">
         <v>-4.59</v>
       </c>
-      <c r="T16" s="183">
-        <v>14.74</v>
+      <c r="T16" s="187">
+        <v>12.41</v>
       </c>
     </row>
     <row r="17">
@@ -4877,40 +4877,40 @@
       <c r="F18" t="str"/>
       <c r="G18" t="str"/>
       <c r="H18" t="str"/>
-      <c r="I18" s="204">
+      <c r="I18" s="199">
         <v>40</v>
       </c>
-      <c r="J18" s="200">
+      <c r="J18" s="196">
         <v>60</v>
       </c>
-      <c r="K18" s="198">
+      <c r="K18" s="200">
         <v>53.33</v>
       </c>
-      <c r="L18" s="201">
+      <c r="L18" s="204">
         <v>46.67</v>
       </c>
-      <c r="M18" s="206">
+      <c r="M18" s="197">
         <v>53.33</v>
       </c>
-      <c r="N18" s="199">
+      <c r="N18" s="198">
         <v>53.33</v>
       </c>
-      <c r="O18" s="202">
+      <c r="O18" s="201">
         <v>53.33</v>
       </c>
-      <c r="P18" s="207">
+      <c r="P18" s="202">
         <v>60</v>
       </c>
       <c r="Q18" s="205">
         <v>53.33</v>
       </c>
-      <c r="R18" s="196">
+      <c r="R18" s="206">
         <v>53.33</v>
       </c>
-      <c r="S18" s="197">
+      <c r="S18" s="203">
         <v>53.33</v>
       </c>
-      <c r="T18" s="203">
+      <c r="T18" s="207">
         <v>53.33</v>
       </c>
     </row>
@@ -4925,41 +4925,41 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="211">
+      <c r="I19" s="209">
         <v>3.7</v>
       </c>
-      <c r="J19" s="219">
+      <c r="J19" s="217">
         <v>3.35</v>
       </c>
-      <c r="K19" s="213">
+      <c r="K19" s="210">
         <v>2.78</v>
       </c>
-      <c r="L19" s="208">
+      <c r="L19" s="218">
         <v>3.08</v>
       </c>
-      <c r="M19" s="215">
+      <c r="M19" s="212">
         <v>5.09</v>
       </c>
-      <c r="N19" s="214">
+      <c r="N19" s="213">
         <v>4.08</v>
       </c>
-      <c r="O19" s="216">
+      <c r="O19" s="214">
         <v>5.66</v>
       </c>
-      <c r="P19" s="209">
+      <c r="P19" s="215">
         <v>9.79</v>
       </c>
-      <c r="Q19" s="217">
+      <c r="Q19" s="219">
         <v>11.41</v>
       </c>
-      <c r="R19" s="218">
+      <c r="R19" s="211">
         <v>13.65</v>
       </c>
-      <c r="S19" s="212">
+      <c r="S19" s="208">
         <v>17.55</v>
       </c>
-      <c r="T19" s="210">
-        <v>0.73</v>
+      <c r="T19" s="216">
+        <v>0.42</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/落升(江南神鹰)/index.xlsx
+++ b/youzi/落升(江南神鹰)/index.xlsx
@@ -39,6 +39,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
@@ -63,30 +69,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3949"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -99,805 +123,1201 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF98D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4957"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF98D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD83343"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25B68"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD3EDD9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA8AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B9BF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8236"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D2A0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5DBD73"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD2303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4FB767"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEDDB9"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA8DBB4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7BC98D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77883"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF31AB4D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0E5C8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF66C07B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDBF0E0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196D2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE04E5C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE404F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B8BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D4D7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE46370"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC32938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7ECA8F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259D41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF90D19F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8537"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD63242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF39AE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7130"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9DDE0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC72B3A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD83343"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25B68"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B9BF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA8AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D2A0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF5DBD73"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD2303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBC2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAEDDB9"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7BC98D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4FB767"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77883"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA8DBB4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF31AB4D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0E5C8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF66C07B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDBF0E0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196D2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -909,439 +1329,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE404F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE46370"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE04E5C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B8BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF90D19F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF7ECA8F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259D41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8537"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD63242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7130"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF39AE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D4D7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3898,7 +3898,7 @@
       <c r="C2" t="str">
         <v>603636</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="1" t="str">
         <v>净买: 1815.37万</v>
       </c>
       <c r="E2">
@@ -3913,41 +3913,41 @@
       <c r="H2">
         <v>10.02</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="2">
         <v>0</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="3">
         <v>2.04</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="12">
         <v>4.88</v>
       </c>
       <c r="L2" s="6">
         <v>7.07</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="4">
         <v>7.94</v>
       </c>
-      <c r="N2" s="12">
+      <c r="N2" s="7">
         <v>10.06</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="8">
         <v>21.06</v>
       </c>
-      <c r="P2" s="7">
+      <c r="P2" s="13">
         <v>33.16</v>
       </c>
-      <c r="Q2" s="8">
+      <c r="Q2" s="5">
         <v>23.03</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="9">
         <v>25.8</v>
       </c>
-      <c r="S2" s="9">
+      <c r="S2" s="10">
         <v>24.05</v>
       </c>
-      <c r="T2" s="10">
-        <v>-33.89</v>
+      <c r="T2" s="11">
+        <v>-36.08</v>
       </c>
     </row>
     <row r="3">
@@ -3960,7 +3960,7 @@
       <c r="C3" t="str">
         <v>605588</v>
       </c>
-      <c r="D3" s="17" t="str">
+      <c r="D3" s="24" t="str">
         <v>净买: 1980.32万</v>
       </c>
       <c r="E3">
@@ -3975,41 +3975,41 @@
       <c r="H3">
         <v>10.01</v>
       </c>
-      <c r="I3" s="23">
+      <c r="I3" s="16">
         <v>0</v>
       </c>
-      <c r="J3" s="18">
+      <c r="J3" s="19">
         <v>6.96</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="17">
         <v>6.11</v>
       </c>
-      <c r="L3" s="15">
+      <c r="L3" s="20">
         <v>-2.38</v>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="25">
         <v>-10.29</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="21">
         <v>-19.26</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="26">
         <v>-18.34</v>
       </c>
-      <c r="P3" s="22">
+      <c r="P3" s="18">
         <v>-18.05</v>
       </c>
-      <c r="Q3" s="20">
+      <c r="Q3" s="14">
         <v>-17.13</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="15">
         <v>-13.31</v>
       </c>
-      <c r="S3" s="26">
+      <c r="S3" s="23">
         <v>-13.66</v>
       </c>
-      <c r="T3" s="14">
-        <v>6.13</v>
+      <c r="T3" s="22">
+        <v>4.49</v>
       </c>
     </row>
     <row r="4">
@@ -4022,7 +4022,7 @@
       <c r="C4" t="str">
         <v>002165</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 3957.43万</v>
       </c>
       <c r="E4">
@@ -4037,41 +4037,41 @@
       <c r="H4">
         <v>-10.02</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="27">
         <v>22.26</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="30">
         <v>16.61</v>
       </c>
-      <c r="K4" s="32">
+      <c r="K4" s="35">
         <v>28.28</v>
       </c>
-      <c r="L4" s="38">
+      <c r="L4" s="31">
         <v>18.25</v>
       </c>
-      <c r="M4" s="39">
+      <c r="M4" s="36">
         <v>30.11</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="32">
         <v>29.56</v>
       </c>
-      <c r="O4" s="27">
+      <c r="O4" s="39">
         <v>32.48</v>
       </c>
-      <c r="P4" s="35">
+      <c r="P4" s="33">
         <v>40.15</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="Q4" s="37">
         <v>48.54</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="38">
         <v>63.32</v>
       </c>
       <c r="S4" s="28">
         <v>79.74</v>
       </c>
       <c r="T4" s="29">
-        <v>60.04</v>
+        <v>58.94</v>
       </c>
     </row>
     <row r="5">
@@ -4084,7 +4084,7 @@
       <c r="C5" t="str">
         <v>002165</v>
       </c>
-      <c r="D5" s="46" t="str">
+      <c r="D5" s="44" t="str">
         <v>净卖: -4519.88万</v>
       </c>
       <c r="E5">
@@ -4099,41 +4099,41 @@
       <c r="H5">
         <v>-8.21</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="52">
         <v>3.9</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="45">
         <v>14.31</v>
       </c>
-      <c r="K5" s="43">
+      <c r="K5" s="46">
         <v>5.37</v>
       </c>
-      <c r="L5" s="44">
+      <c r="L5" s="48">
         <v>15.93</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="40">
         <v>15.45</v>
       </c>
-      <c r="N5" s="52">
+      <c r="N5" s="41">
         <v>18.05</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="43">
         <v>24.88</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="49">
         <v>32.36</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="50">
         <v>45.53</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="47">
         <v>60.16</v>
       </c>
-      <c r="S5" s="50">
+      <c r="S5" s="42">
         <v>76.26</v>
       </c>
       <c r="T5" s="51">
-        <v>42.6</v>
+        <v>41.63</v>
       </c>
     </row>
     <row r="6">
@@ -4146,7 +4146,7 @@
       <c r="C6" t="str">
         <v>002688</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="64" t="str">
         <v>净买: 1976.41万</v>
       </c>
       <c r="E6">
@@ -4164,38 +4164,38 @@
       <c r="I6" s="65">
         <v>0</v>
       </c>
-      <c r="J6" s="61">
+      <c r="J6" s="56">
         <v>9.93</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="57">
         <v>20.88</v>
       </c>
       <c r="L6" s="58">
         <v>33</v>
       </c>
-      <c r="M6" s="54">
+      <c r="M6" s="59">
         <v>43.1</v>
       </c>
-      <c r="N6" s="55">
+      <c r="N6" s="62">
         <v>28.79</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="54">
         <v>19.36</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="63">
         <v>21.55</v>
       </c>
-      <c r="Q6" s="60">
+      <c r="Q6" s="53">
         <v>9.43</v>
       </c>
-      <c r="R6" s="56">
+      <c r="R6" s="55">
         <v>4.04</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="60">
         <v>4.38</v>
       </c>
-      <c r="T6" s="57">
-        <v>-2.02</v>
+      <c r="T6" s="61">
+        <v>-1.01</v>
       </c>
     </row>
     <row r="7">
@@ -4208,7 +4208,7 @@
       <c r="C7" t="str">
         <v>002165</v>
       </c>
-      <c r="D7" s="74" t="str">
+      <c r="D7" s="70" t="str">
         <v>净卖: -2117.52万</v>
       </c>
       <c r="E7">
@@ -4223,41 +4223,41 @@
       <c r="H7">
         <v>7.72</v>
       </c>
-      <c r="I7" s="75">
+      <c r="I7" s="71">
         <v>2.15</v>
       </c>
-      <c r="J7" s="67">
+      <c r="J7" s="74">
         <v>1.72</v>
       </c>
       <c r="K7" s="72">
         <v>4.01</v>
       </c>
-      <c r="L7" s="70">
+      <c r="L7" s="77">
         <v>10.03</v>
       </c>
-      <c r="M7" s="73">
+      <c r="M7" s="78">
         <v>16.62</v>
       </c>
-      <c r="N7" s="76">
+      <c r="N7" s="75">
         <v>28.22</v>
       </c>
-      <c r="O7" s="68">
+      <c r="O7" s="76">
         <v>41.12</v>
       </c>
-      <c r="P7" s="77">
+      <c r="P7" s="73">
         <v>55.3</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="66">
         <v>70.77</v>
       </c>
-      <c r="R7" s="69">
+      <c r="R7" s="67">
         <v>73.21</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="69">
         <v>90.54</v>
       </c>
-      <c r="T7" s="66">
-        <v>25.64</v>
+      <c r="T7" s="68">
+        <v>24.79</v>
       </c>
     </row>
     <row r="8">
@@ -4270,7 +4270,7 @@
       <c r="C8" t="str">
         <v>002923</v>
       </c>
-      <c r="D8" s="89" t="str">
+      <c r="D8" s="87" t="str">
         <v>净买: 1689.05万</v>
       </c>
       <c r="E8">
@@ -4285,41 +4285,41 @@
       <c r="H8">
         <v>-5.06</v>
       </c>
-      <c r="I8" s="81">
+      <c r="I8" s="91">
         <v>-5.2</v>
       </c>
-      <c r="J8" s="84">
+      <c r="J8" s="88">
         <v>-2.53</v>
       </c>
-      <c r="K8" s="85">
+      <c r="K8" s="89">
         <v>-6.53</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="79">
         <v>-6.07</v>
       </c>
-      <c r="M8" s="86">
+      <c r="M8" s="90">
         <v>-4.07</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="84">
         <v>-13.67</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="80">
         <v>-17</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="81">
         <v>-19.33</v>
       </c>
-      <c r="Q8" s="79">
+      <c r="Q8" s="82">
         <v>-16</v>
       </c>
-      <c r="R8" s="83">
+      <c r="R8" s="85">
         <v>-17.47</v>
       </c>
-      <c r="S8" s="80">
+      <c r="S8" s="86">
         <v>-15</v>
       </c>
-      <c r="T8" s="91">
-        <v>-16.4</v>
+      <c r="T8" s="83">
+        <v>-8.07</v>
       </c>
     </row>
     <row r="9">
@@ -4332,7 +4332,7 @@
       <c r="C9" t="str">
         <v>000965</v>
       </c>
-      <c r="D9" s="104" t="str">
+      <c r="D9" s="100" t="str">
         <v>净卖: -66.63万</v>
       </c>
       <c r="E9">
@@ -4347,19 +4347,19 @@
       <c r="H9">
         <v>0.31</v>
       </c>
-      <c r="I9" s="96">
+      <c r="I9" s="92">
         <v>8.75</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="96">
         <v>-1.56</v>
       </c>
-      <c r="K9" s="98">
+      <c r="K9" s="93">
         <v>-0.94</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="97">
         <v>-3.75</v>
       </c>
-      <c r="M9" s="99">
+      <c r="M9" s="101">
         <v>5.94</v>
       </c>
       <c r="N9" s="94">
@@ -4368,20 +4368,20 @@
       <c r="O9" s="102">
         <v>28.12</v>
       </c>
-      <c r="P9" s="97">
+      <c r="P9" s="98">
         <v>40.94</v>
       </c>
-      <c r="Q9" s="100">
+      <c r="Q9" s="103">
         <v>55</v>
       </c>
-      <c r="R9" s="95">
+      <c r="R9" s="104">
         <v>48.12</v>
       </c>
-      <c r="S9" s="103">
+      <c r="S9" s="99">
         <v>62.81</v>
       </c>
-      <c r="T9" s="101">
-        <v>11.87</v>
+      <c r="T9" s="95">
+        <v>10.94</v>
       </c>
     </row>
     <row r="10">
@@ -4409,41 +4409,41 @@
       <c r="H10">
         <v>10.02</v>
       </c>
-      <c r="I10" s="106">
+      <c r="I10" s="105">
         <v>-0.74</v>
       </c>
-      <c r="J10" s="111">
+      <c r="J10" s="114">
         <v>-10.6</v>
       </c>
-      <c r="K10" s="112">
+      <c r="K10" s="111">
         <v>-14.1</v>
       </c>
-      <c r="L10" s="108">
+      <c r="L10" s="106">
         <v>-12.78</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="108">
         <v>-4.07</v>
       </c>
-      <c r="N10" s="109">
+      <c r="N10" s="115">
         <v>-3.06</v>
       </c>
-      <c r="O10" s="116">
+      <c r="O10" s="107">
         <v>-6.09</v>
       </c>
-      <c r="P10" s="114">
+      <c r="P10" s="116">
         <v>3.33</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="112">
         <v>-2.01</v>
       </c>
-      <c r="R10" s="107">
+      <c r="R10" s="109">
         <v>-1.88</v>
       </c>
       <c r="S10" s="117">
         <v>-4.77</v>
       </c>
-      <c r="T10" s="105">
-        <v>8.01</v>
+      <c r="T10" s="113">
+        <v>14.32</v>
       </c>
     </row>
     <row r="11">
@@ -4456,7 +4456,7 @@
       <c r="C11" t="str">
         <v>600794</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="118" t="str">
         <v>净卖: -697.77万</v>
       </c>
       <c r="E11">
@@ -4471,41 +4471,41 @@
       <c r="H11">
         <v>-8.75</v>
       </c>
-      <c r="I11" s="118">
+      <c r="I11" s="119">
         <v>-1.46</v>
       </c>
-      <c r="J11" s="125">
+      <c r="J11" s="124">
         <v>-11.25</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="125">
         <v>-17.08</v>
       </c>
-      <c r="L11" s="119">
+      <c r="L11" s="128">
         <v>-14.37</v>
       </c>
-      <c r="M11" s="120">
+      <c r="M11" s="126">
         <v>-11.67</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="122">
         <v>-12.71</v>
       </c>
-      <c r="O11" s="122">
+      <c r="O11" s="123">
         <v>-15.42</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="120">
         <v>-15.42</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="129">
         <v>-12.29</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="121">
         <v>-3.54</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="130">
         <v>-0.83</v>
       </c>
-      <c r="T11" s="130">
-        <v>-25</v>
+      <c r="T11" s="127">
+        <v>-26.67</v>
       </c>
     </row>
     <row r="12">
@@ -4518,7 +4518,7 @@
       <c r="C12" t="str">
         <v>000627</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="143" t="str">
         <v>净买: 1535.97万</v>
       </c>
       <c r="E12">
@@ -4533,28 +4533,28 @@
       <c r="H12">
         <v>-9.87</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="131">
         <v>0</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="132">
         <v>-5.11</v>
       </c>
       <c r="K12" s="139">
         <v>-9.85</v>
       </c>
-      <c r="L12" s="135">
+      <c r="L12" s="134">
         <v>-14.23</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="135">
         <v>-18.61</v>
       </c>
-      <c r="N12" s="136">
+      <c r="N12" s="140">
         <v>-22.63</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="136">
         <v>-26.64</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="141">
         <v>-30.29</v>
       </c>
       <c r="Q12" s="137">
@@ -4563,10 +4563,10 @@
       <c r="R12" s="138">
         <v>-36.86</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="133">
         <v>-36.86</v>
       </c>
-      <c r="T12" s="141">
+      <c r="T12" s="142">
         <v>-42.34</v>
       </c>
     </row>
@@ -4580,7 +4580,7 @@
       <c r="C13" t="str">
         <v>603669</v>
       </c>
-      <c r="D13" s="144" t="str">
+      <c r="D13" s="145" t="str">
         <v>净卖: -338.04万</v>
       </c>
       <c r="E13">
@@ -4595,41 +4595,41 @@
       <c r="H13">
         <v>0.7</v>
       </c>
-      <c r="I13" s="145">
+      <c r="I13" s="146">
         <v>9.25</v>
       </c>
-      <c r="J13" s="152">
+      <c r="J13" s="154">
         <v>9.77</v>
       </c>
-      <c r="K13" s="150">
+      <c r="K13" s="147">
         <v>10.65</v>
       </c>
-      <c r="L13" s="146">
+      <c r="L13" s="155">
         <v>8.9</v>
       </c>
-      <c r="M13" s="147">
+      <c r="M13" s="148">
         <v>8.2</v>
       </c>
-      <c r="N13" s="153">
+      <c r="N13" s="156">
         <v>7.33</v>
       </c>
-      <c r="O13" s="155">
+      <c r="O13" s="149">
         <v>4.36</v>
       </c>
-      <c r="P13" s="156">
+      <c r="P13" s="151">
         <v>1.75</v>
       </c>
-      <c r="Q13" s="154">
+      <c r="Q13" s="152">
         <v>1.05</v>
       </c>
-      <c r="R13" s="148">
+      <c r="R13" s="150">
         <v>4.71</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="153">
         <v>3.84</v>
       </c>
-      <c r="T13" s="151">
-        <v>-25.48</v>
+      <c r="T13" s="144">
+        <v>-23.91</v>
       </c>
     </row>
     <row r="14">
@@ -4642,7 +4642,7 @@
       <c r="C14" t="str">
         <v>000029</v>
       </c>
-      <c r="D14" s="159" t="str">
+      <c r="D14" s="158" t="str">
         <v>净卖: -639.40万</v>
       </c>
       <c r="E14">
@@ -4657,41 +4657,41 @@
       <c r="H14">
         <v>-9.37</v>
       </c>
-      <c r="I14" s="162">
+      <c r="I14" s="161">
         <v>-0.7</v>
       </c>
-      <c r="J14" s="163">
+      <c r="J14" s="159">
         <v>-3</v>
       </c>
-      <c r="K14" s="166">
+      <c r="K14" s="162">
         <v>-4.4</v>
       </c>
-      <c r="L14" s="160">
+      <c r="L14" s="166">
         <v>-2.57</v>
       </c>
-      <c r="M14" s="157">
+      <c r="M14" s="163">
         <v>-6.27</v>
       </c>
-      <c r="N14" s="164">
+      <c r="N14" s="167">
         <v>-6.34</v>
       </c>
-      <c r="O14" s="165">
+      <c r="O14" s="164">
         <v>-10.14</v>
       </c>
-      <c r="P14" s="167">
+      <c r="P14" s="165">
         <v>-5.84</v>
       </c>
       <c r="Q14" s="168">
         <v>-7.84</v>
       </c>
-      <c r="R14" s="169">
+      <c r="R14" s="160">
         <v>-9.34</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="157">
         <v>-8.27</v>
       </c>
-      <c r="T14" s="158">
-        <v>-30.82</v>
+      <c r="T14" s="169">
+        <v>-32.12</v>
       </c>
     </row>
     <row r="15">
@@ -4704,7 +4704,7 @@
       <c r="C15" t="str">
         <v>002856</v>
       </c>
-      <c r="D15" s="176" t="str">
+      <c r="D15" s="180" t="str">
         <v>净买: 611.16万</v>
       </c>
       <c r="E15">
@@ -4719,31 +4719,31 @@
       <c r="H15">
         <v>-6.28</v>
       </c>
-      <c r="I15" s="171">
+      <c r="I15" s="178">
         <v>17.36</v>
       </c>
-      <c r="J15" s="180">
+      <c r="J15" s="172">
         <v>12.95</v>
       </c>
-      <c r="K15" s="182">
+      <c r="K15" s="181">
         <v>15.42</v>
       </c>
-      <c r="L15" s="177">
+      <c r="L15" s="179">
         <v>15.86</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="176">
         <v>13.22</v>
       </c>
-      <c r="N15" s="179">
+      <c r="N15" s="182">
         <v>9.87</v>
       </c>
-      <c r="O15" s="170">
+      <c r="O15" s="177">
         <v>15.95</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="170">
         <v>16.56</v>
       </c>
-      <c r="Q15" s="172">
+      <c r="Q15" s="171">
         <v>14.8</v>
       </c>
       <c r="R15" s="173">
@@ -4766,7 +4766,7 @@
       <c r="C16" t="str">
         <v>603017</v>
       </c>
-      <c r="D16" s="191" t="str">
+      <c r="D16" s="189" t="str">
         <v>净买: 1022.95万</v>
       </c>
       <c r="E16">
@@ -4781,41 +4781,41 @@
       <c r="H16">
         <v>10.01</v>
       </c>
-      <c r="I16" s="192">
+      <c r="I16" s="186">
         <v>0</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="190">
         <v>10</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="191">
         <v>-0.98</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="192">
         <v>-6.69</v>
       </c>
-      <c r="M16" s="183">
+      <c r="M16" s="185">
         <v>-9.32</v>
       </c>
-      <c r="N16" s="188">
+      <c r="N16" s="195">
         <v>-9.55</v>
       </c>
-      <c r="O16" s="194">
+      <c r="O16" s="193">
         <v>-8.87</v>
       </c>
-      <c r="P16" s="186">
+      <c r="P16" s="183">
         <v>-9.25</v>
       </c>
-      <c r="Q16" s="189">
+      <c r="Q16" s="187">
         <v>-7.74</v>
       </c>
-      <c r="R16" s="195">
+      <c r="R16" s="194">
         <v>-3.68</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="184">
         <v>-4.59</v>
       </c>
-      <c r="T16" s="187">
-        <v>12.41</v>
+      <c r="T16" s="188">
+        <v>4.51</v>
       </c>
     </row>
     <row r="17">
@@ -4877,40 +4877,40 @@
       <c r="F18" t="str"/>
       <c r="G18" t="str"/>
       <c r="H18" t="str"/>
-      <c r="I18" s="199">
+      <c r="I18" s="203">
         <v>40</v>
       </c>
-      <c r="J18" s="196">
+      <c r="J18" s="206">
         <v>60</v>
       </c>
-      <c r="K18" s="200">
+      <c r="K18" s="207">
         <v>53.33</v>
       </c>
-      <c r="L18" s="204">
+      <c r="L18" s="196">
         <v>46.67</v>
       </c>
-      <c r="M18" s="197">
+      <c r="M18" s="200">
         <v>53.33</v>
       </c>
-      <c r="N18" s="198">
+      <c r="N18" s="201">
         <v>53.33</v>
       </c>
-      <c r="O18" s="201">
+      <c r="O18" s="204">
         <v>53.33</v>
       </c>
-      <c r="P18" s="202">
+      <c r="P18" s="197">
         <v>60</v>
       </c>
-      <c r="Q18" s="205">
+      <c r="Q18" s="202">
         <v>53.33</v>
       </c>
-      <c r="R18" s="206">
+      <c r="R18" s="199">
         <v>53.33</v>
       </c>
-      <c r="S18" s="203">
+      <c r="S18" s="198">
         <v>53.33</v>
       </c>
-      <c r="T18" s="207">
+      <c r="T18" s="205">
         <v>53.33</v>
       </c>
     </row>
@@ -4925,41 +4925,41 @@
       <c r="F19" t="str"/>
       <c r="G19" t="str"/>
       <c r="H19" t="str"/>
-      <c r="I19" s="209">
+      <c r="I19" s="215">
         <v>3.7</v>
       </c>
-      <c r="J19" s="217">
+      <c r="J19" s="208">
         <v>3.35</v>
       </c>
-      <c r="K19" s="210">
+      <c r="K19" s="211">
         <v>2.78</v>
       </c>
-      <c r="L19" s="218">
+      <c r="L19" s="209">
         <v>3.08</v>
       </c>
-      <c r="M19" s="212">
+      <c r="M19" s="218">
         <v>5.09</v>
       </c>
-      <c r="N19" s="213">
+      <c r="N19" s="219">
         <v>4.08</v>
       </c>
-      <c r="O19" s="214">
+      <c r="O19" s="212">
         <v>5.66</v>
       </c>
-      <c r="P19" s="215">
+      <c r="P19" s="216">
         <v>9.79</v>
       </c>
-      <c r="Q19" s="219">
+      <c r="Q19" s="213">
         <v>11.41</v>
       </c>
-      <c r="R19" s="211">
+      <c r="R19" s="217">
         <v>13.65</v>
       </c>
-      <c r="S19" s="208">
+      <c r="S19" s="214">
         <v>17.55</v>
       </c>
-      <c r="T19" s="216">
-        <v>0.42</v>
+      <c r="T19" s="210">
+        <v>0.33</v>
       </c>
     </row>
   </sheetData>
